--- a/outputs/coverage/pokrytie_po_brendam_2026-06-30.xlsx
+++ b/outputs/coverage/pokrytie_po_brendam_2026-06-30.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Покрытие" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Новый контейнер" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +33,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C55A11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +60,11 @@
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C55A11"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -68,13 +78,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5582,7 +5596,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
           <t>SKIN1004 Madagascar Centella Ampoule 55ml</t>
@@ -5619,7 +5632,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
           <t>Пенка для умыванияCELIMAX THE REAL NONI ACNE BUBBLE CLEANSER</t>
@@ -5656,7 +5668,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
           <t>Сыворотка-лифтинг с ПДРН и пептидами Medicube, 30 мл/PDRN PI</t>
@@ -5693,7 +5704,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
           <t xml:space="preserve">1025 DOKDO BUBBLE FOAM_150ml (дозатор ) </t>
@@ -5730,7 +5740,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
           <t>Блеск Плампер для губ VT REEDLE SHOT LIP PLUMPER EXPERT</t>
@@ -5767,7 +5776,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
           <t>Гель для душа от прыщей с кислотами/PINE CALMING CICA BODY W</t>
@@ -5804,7 +5812,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
           <t xml:space="preserve">Сыворотка для лица от морщин с микроиглами 7500 и пдрн/PDRN </t>
@@ -5841,7 +5848,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
           <t>Осветляющий Крем от пигментации с Транексамовой Кислотой/[De</t>
@@ -5878,7 +5884,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
           <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]</t>
@@ -5915,7 +5920,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
           <t>Увлажняющий тонер-эссенция для лица с аденозином 7500 ppm/Ad</t>
@@ -5952,7 +5956,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
           <t xml:space="preserve">CELIMAX DUAL BARRIER MILD GEL CLEANSER 200ML(дозатор) </t>
@@ -5989,7 +5992,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
           <t>CELIMAX OIL CONTROL MOISTURIZING CREAM 80ML</t>
@@ -6026,7 +6028,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
           <t xml:space="preserve">Сыворотка с пептидами Матриксил 15% от морщин/ </t>
@@ -6063,7 +6064,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
           <t>SKIN1004 Madagascar Centella Soothing Cream 75ml</t>
@@ -6100,7 +6100,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
           <t>BIFIDA BIOME AMPOULE TONER 210 мл</t>
@@ -6137,7 +6136,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
           <t>CELIMAX PORE+DARK SPOT BRIGHTENING KIT</t>
@@ -6174,7 +6172,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
           <t>Тонер  для лица увлажняющий от прыщей Корея/EXOSOME CICA TON</t>
@@ -6211,7 +6208,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI REFRESH CLAY MASK 120G</t>
@@ -6248,7 +6244,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI CALMING GLOW PAD 50PADS,</t>
@@ -6285,7 +6280,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
           <t>VT REEDLE SHOT LIFTING EYE CREAM</t>
@@ -6322,7 +6316,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
           <t>CELIMAX DERMA NATURE GLUTATHIONE LONGLASTING TONE-UP CREAM 3</t>
@@ -6359,7 +6352,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
           <t xml:space="preserve">Крем для лица увлажняющий для проблемной кожи с сосной/PINE </t>
@@ -6396,7 +6388,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
           <t>DEOPROCE SHAMPOO - ARGAN SILKY MOISTURE</t>
@@ -6433,7 +6424,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
           <t>CELIMAX JI WOO GAE CICA BHA ACNE FOAM CLEANSING 150ML</t>
@@ -6470,7 +6460,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
           <t>Крем для лица c Бакучиолом и Микроиглами от морщин/ Bakuchio</t>
@@ -6507,7 +6496,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL CICA SOOTHING CREAM 50ML</t>
@@ -6544,7 +6532,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
           <t>Крем для лица укрепляющий с ретиналем 300ppm/[Derma Factory]</t>
@@ -6581,7 +6568,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
           <t>Интенсивная антивозрастная сыворотка для лица PDRN 4%, 30 мл</t>
@@ -6618,7 +6604,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
           <t>Сыворотка для лица осветляющая от пигментации/[Derma Factory</t>
@@ -6655,7 +6640,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
           <t>CELIMAX DERMA NATURE RELIEF MADECICA PH BALANCING FOAM CLEAN</t>
@@ -6692,7 +6676,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
           <t xml:space="preserve">SOYBEAN SERUM_50ml/Сыворотка для лица увлажняющая от морщин </t>
@@ -6729,7 +6712,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
           <t>CELIMAX JI WOO GAE ONE STEP MILD CLEANSING PAD 60PADS</t>
@@ -6766,7 +6748,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
           <t>ROUND LAB CAMELLIA DEEP COLLAGEN FIRMING CREAM_50ml</t>
@@ -6803,7 +6784,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
           <t>CELIMAX OIL CONTROL CAPSULE ESSENCE 30ML</t>
@@ -6840,7 +6820,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL CICA NIACINAMIDE AC CALMING SERUM 40ML</t>
@@ -6877,7 +6856,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
           <t>Пенка очищающая для лица от прыщей с сосной и кислотами/PINE</t>
@@ -6914,7 +6892,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
           <t>1025 DOKDO CREAM_80ml</t>
@@ -6951,7 +6928,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
           <t xml:space="preserve">Сыворотка для лица от морщин с микроиглами 2000 и пдрн/PDRN </t>
@@ -6988,7 +6964,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
           <t>Крем для лица увлажняющий капсульный /PDRN PINK COLLAGEN CAP</t>
@@ -7025,7 +7000,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
           <t>капсульный крем для лица /TXA NIACINAMIDE CAPSULE CREAM 55g</t>
@@ -7062,7 +7036,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
           <t>ROUND LAB STICK POUCH KIT(Набор саше миниатюр для лица 12 шт</t>
@@ -7099,7 +7072,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
           <t>CELIMAX ONE STEP BODY BRIGHTENING PAD 60PADS</t>
@@ -7136,7 +7108,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
           <t>SKIN1004 Madagascar Centella Tone Brightening Capsule Ampoul</t>
@@ -7173,7 +7144,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
         <is>
           <t>CELIMAX THE REAL NONI ENERGY REPAIR CREAM 50ML</t>
@@ -7210,7 +7180,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
           <t>PDRN PINK HYALURONIC MOISTURIZING CREAM 50ml</t>
@@ -7247,7 +7216,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
           <t>Антивозрастная сыворотка-стик для лица с волюфилином</t>
@@ -7284,7 +7252,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
           <t>Сыворотка с Ниацинамидом для лица от прыщей Niacinamide/[Der</t>
@@ -7321,7 +7288,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
           <t>PINE CALMING CICA PAD_50pcs/Тонер пэды диски для лица от пры</t>
@@ -7358,7 +7324,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
           <t>Гидрофильное масло CELIMAX DERMA NATURE FRESH BLACKHEAD JOJO</t>
@@ -7395,7 +7360,6 @@
           <t>НОВЫЕ/ПРОЧЕЕ</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
           <t>Тонер пэды для лица,60 шт CELIMAX JI WOO GAE HEARTLEAF BHA P</t>
@@ -7438,4 +7402,1749 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Транзит, мес</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Бренд</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Артикул</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Итого сейчас</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Продажи/мес</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Спрос 2маг/мес</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Хватит дней</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>В контейнер, шт</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Вес, т</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>551465879</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4856</v>
+      </c>
+      <c r="E3" t="n">
+        <v>618</v>
+      </c>
+      <c r="F3">
+        <f>E3*$J$3</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>IF(F3=0,"",ROUND(D3/(F3/30),0))</f>
+        <v/>
+      </c>
+      <c r="H3">
+        <f>MAX(0,ROUND(F3*$J$2-D3,0))</f>
+        <v/>
+      </c>
+      <c r="I3" s="1">
+        <f>H3*$J$4/1000</f>
+        <v/>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>238358954</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ENOUGH - Collagen 3in1 Sun Cream SPF50 PA+++ [50ml] / о</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>318</v>
+      </c>
+      <c r="E4" t="n">
+        <v>539</v>
+      </c>
+      <c r="F4">
+        <f>E4*$J$3</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>IF(F4=0,"",ROUND(D4/(F4/30),0))</f>
+        <v/>
+      </c>
+      <c r="H4">
+        <f>MAX(0,ROUND(F4*$J$2-D4,0))</f>
+        <v/>
+      </c>
+      <c r="I4" s="1">
+        <f>H4*$J$4/1000</f>
+        <v/>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>207796789</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13] / Тон</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1036</v>
+      </c>
+      <c r="E5" t="n">
+        <v>306</v>
+      </c>
+      <c r="F5">
+        <f>E5*$J$3</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>IF(F5=0,"",ROUND(D5/(F5/30),0))</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>MAX(0,ROUND(F5*$J$2-D5,0))</f>
+        <v/>
+      </c>
+      <c r="I5" s="1">
+        <f>H5*$J$4/1000</f>
+        <v/>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>198156472</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1142</v>
+      </c>
+      <c r="E6" t="n">
+        <v>237</v>
+      </c>
+      <c r="F6">
+        <f>E6*$J$3</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>IF(F6=0,"",ROUND(D6/(F6/30),0))</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>MAX(0,ROUND(F6*$J$2-D6,0))</f>
+        <v/>
+      </c>
+      <c r="I6" s="1">
+        <f>H6*$J$4/1000</f>
+        <v/>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>207483179</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица у</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1540</v>
+      </c>
+      <c r="E7" t="n">
+        <v>212</v>
+      </c>
+      <c r="F7">
+        <f>E7*$J$3</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>IF(F7=0,"",ROUND(D7/(F7/30),0))</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>MAX(0,ROUND(F7*$J$2-D7,0))</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>H7*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>151175880</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1185</v>
+      </c>
+      <c r="E8" t="n">
+        <v>185</v>
+      </c>
+      <c r="F8">
+        <f>E8*$J$3</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IF(F8=0,"",ROUND(D8/(F8/30),0))</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>MAX(0,ROUND(F8*$J$2-D8,0))</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>H8*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>207796898</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21] / Тон</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>684</v>
+      </c>
+      <c r="E9" t="n">
+        <v>175</v>
+      </c>
+      <c r="F9">
+        <f>E9*$J$3</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>IF(F9=0,"",ROUND(D9/(F9/30),0))</f>
+        <v/>
+      </c>
+      <c r="H9">
+        <f>MAX(0,ROUND(F9*$J$2-D9,0))</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>H9*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>207796563</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA - Aqua Hyaluronic Acid Water Drop Cream / Ув</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>45</v>
+      </c>
+      <c r="E10" t="n">
+        <v>171</v>
+      </c>
+      <c r="F10">
+        <f>E10*$J$3</f>
+        <v/>
+      </c>
+      <c r="G10">
+        <f>IF(F10=0,"",ROUND(D10/(F10/30),0))</f>
+        <v/>
+      </c>
+      <c r="H10">
+        <f>MAX(0,ROUND(F10*$J$2-D10,0))</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>H10*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>170198337</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ENOUGH - Premium 8 Peptide Full Cover Perfect Foundatio</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>632</v>
+      </c>
+      <c r="E11" t="n">
+        <v>160</v>
+      </c>
+      <c r="F11">
+        <f>E11*$J$3</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>IF(F11=0,"",ROUND(D11/(F11/30),0))</f>
+        <v/>
+      </c>
+      <c r="H11">
+        <f>MAX(0,ROUND(F11*$J$2-D11,0))</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>H11*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>226115324</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Ох</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1197</v>
+      </c>
+      <c r="E12" t="n">
+        <v>153</v>
+      </c>
+      <c r="F12">
+        <f>E12*$J$3</f>
+        <v/>
+      </c>
+      <c r="G12">
+        <f>IF(F12=0,"",ROUND(D12/(F12/30),0))</f>
+        <v/>
+      </c>
+      <c r="H12">
+        <f>MAX(0,ROUND(F12*$J$2-D12,0))</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>H12*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>170198180</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundat</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>627</v>
+      </c>
+      <c r="E13" t="n">
+        <v>139</v>
+      </c>
+      <c r="F13">
+        <f>E13*$J$3</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>IF(F13=0,"",ROUND(D13/(F13/30),0))</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>MAX(0,ROUND(F13*$J$2-D13,0))</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>H13*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>170198835</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ENOUGH - Premium Ultra X10 Cover Up Collagen Foundation</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>135</v>
+      </c>
+      <c r="F14">
+        <f>E14*$J$3</f>
+        <v/>
+      </c>
+      <c r="G14">
+        <f>IF(F14=0,"",ROUND(D14/(F14/30),0))</f>
+        <v/>
+      </c>
+      <c r="H14">
+        <f>MAX(0,ROUND(F14*$J$2-D14,0))</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>H14*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>170198109</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundat</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>540</v>
+      </c>
+      <c r="E15" t="n">
+        <v>125</v>
+      </c>
+      <c r="F15">
+        <f>E15*$J$3</f>
+        <v/>
+      </c>
+      <c r="G15">
+        <f>IF(F15=0,"",ROUND(D15/(F15/30),0))</f>
+        <v/>
+      </c>
+      <c r="H15">
+        <f>MAX(0,ROUND(F15*$J$2-D15,0))</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>H15*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>207796439</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA - Natural 90% Olive Cleansing Oil / Очищающе</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>122</v>
+      </c>
+      <c r="F16">
+        <f>E16*$J$3</f>
+        <v/>
+      </c>
+      <c r="G16">
+        <f>IF(F16=0,"",ROUND(D16/(F16/30),0))</f>
+        <v/>
+      </c>
+      <c r="H16">
+        <f>MAX(0,ROUND(F16*$J$2-D16,0))</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>H16*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>205054338</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANYO - Bifida Biome Ampoule Toner [400ml] / Ампульный </t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>112</v>
+      </c>
+      <c r="F17">
+        <f>E17*$J$3</f>
+        <v/>
+      </c>
+      <c r="G17">
+        <f>IF(F17=0,"",ROUND(D17/(F17/30),0))</f>
+        <v/>
+      </c>
+      <c r="H17">
+        <f>MAX(0,ROUND(F17*$J$2-D17,0))</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>H17*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>198156698</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>368</v>
+      </c>
+      <c r="E18" t="n">
+        <v>106</v>
+      </c>
+      <c r="F18">
+        <f>E18*$J$3</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>IF(F18=0,"",ROUND(D18/(F18/30),0))</f>
+        <v/>
+      </c>
+      <c r="H18">
+        <f>MAX(0,ROUND(F18*$J$2-D18,0))</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>H18*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>206057411</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA - Hell pore clean up aha fruit toner [ 200ml</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>458</v>
+      </c>
+      <c r="E19" t="n">
+        <v>105</v>
+      </c>
+      <c r="F19">
+        <f>E19*$J$3</f>
+        <v/>
+      </c>
+      <c r="G19">
+        <f>IF(F19=0,"",ROUND(D19/(F19/30),0))</f>
+        <v/>
+      </c>
+      <c r="H19">
+        <f>MAX(0,ROUND(F19*$J$2-D19,0))</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>H19*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>214305722</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO+BALSAM - BLACK GARLIC[2000ml]</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>570</v>
+      </c>
+      <c r="E20" t="n">
+        <v>95</v>
+      </c>
+      <c r="F20">
+        <f>E20*$J$3</f>
+        <v/>
+      </c>
+      <c r="G20">
+        <f>IF(F20=0,"",ROUND(D20/(F20/30),0))</f>
+        <v/>
+      </c>
+      <c r="H20">
+        <f>MAX(0,ROUND(F20*$J$2-D20,0))</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>H20*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>190159348</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ELIZAVECCA - 24K Gold Snail Cleansing Foam [180ml] / Зо</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>45</v>
+      </c>
+      <c r="E21" t="n">
+        <v>95</v>
+      </c>
+      <c r="F21">
+        <f>E21*$J$3</f>
+        <v/>
+      </c>
+      <c r="G21">
+        <f>IF(F21=0,"",ROUND(D21/(F21/30),0))</f>
+        <v/>
+      </c>
+      <c r="H21">
+        <f>MAX(0,ROUND(F21*$J$2-D21,0))</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>H21*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>170198876</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ENOUGH - Premium Ultra X10 Cover Up Collagen Foundation</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>278</v>
+      </c>
+      <c r="E22" t="n">
+        <v>90</v>
+      </c>
+      <c r="F22">
+        <f>E22*$J$3</f>
+        <v/>
+      </c>
+      <c r="G22">
+        <f>IF(F22=0,"",ROUND(D22/(F22/30),0))</f>
+        <v/>
+      </c>
+      <c r="H22">
+        <f>MAX(0,ROUND(F22*$J$2-D22,0))</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>H22*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>226117746</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PETITFEE - Chamomile Lightening Hydrogel Mask Pack [5pc</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>129</v>
+      </c>
+      <c r="E23" t="n">
+        <v>88</v>
+      </c>
+      <c r="F23">
+        <f>E23*$J$3</f>
+        <v/>
+      </c>
+      <c r="G23">
+        <f>IF(F23=0,"",ROUND(D23/(F23/30),0))</f>
+        <v/>
+      </c>
+      <c r="H23">
+        <f>MAX(0,ROUND(F23*$J$2-D23,0))</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>H23*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EKEL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>208202076</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EKEL - Ampule Сream Сollagen [70ml] / Крем для лица амп</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>324</v>
+      </c>
+      <c r="E24" t="n">
+        <v>83</v>
+      </c>
+      <c r="F24">
+        <f>E24*$J$3</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>IF(F24=0,"",ROUND(D24/(F24/30),0))</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>MAX(0,ROUND(F24*$J$2-D24,0))</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>H24*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>437254254</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROUND LAB SOYBEAN PANTHENOL CREAM_80ml - Крем для лица </t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>310</v>
+      </c>
+      <c r="E25" t="n">
+        <v>72</v>
+      </c>
+      <c r="F25">
+        <f>E25*$J$3</f>
+        <v/>
+      </c>
+      <c r="G25">
+        <f>IF(F25=0,"",ROUND(D25/(F25/30),0))</f>
+        <v/>
+      </c>
+      <c r="H25">
+        <f>MAX(0,ROUND(F25*$J$2-D25,0))</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>H25*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>HEIMISH</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>207465786</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HEIMISH - All Clean Balm Mandarin [120ml] / Очищающий г</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>108</v>
+      </c>
+      <c r="E26" t="n">
+        <v>68</v>
+      </c>
+      <c r="F26">
+        <f>E26*$J$3</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>IF(F26=0,"",ROUND(D26/(F26/30),0))</f>
+        <v/>
+      </c>
+      <c r="H26">
+        <f>MAX(0,ROUND(F26*$J$2-D26,0))</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>H26*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ETUDEHOUSE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>154160085</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [24*7ml] / Очищ</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>309</v>
+      </c>
+      <c r="E27" t="n">
+        <v>65</v>
+      </c>
+      <c r="F27">
+        <f>E27*$J$3</f>
+        <v/>
+      </c>
+      <c r="G27">
+        <f>IF(F27=0,"",ROUND(D27/(F27/30),0))</f>
+        <v/>
+      </c>
+      <c r="H27">
+        <f>MAX(0,ROUND(F27*$J$2-D27,0))</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>H27*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>179611318</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60e</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>357</v>
+      </c>
+      <c r="E28" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28">
+        <f>E28*$J$3</f>
+        <v/>
+      </c>
+      <c r="G28">
+        <f>IF(F28=0,"",ROUND(D28/(F28/30),0))</f>
+        <v/>
+      </c>
+      <c r="H28">
+        <f>MAX(0,ROUND(F28*$J$2-D28,0))</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>H28*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ETUDEHOUSE</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>154159632</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ETUDE - Baking Powder BB Deep Cleansing Foam [30ml] / П</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>175</v>
+      </c>
+      <c r="E29" t="n">
+        <v>50</v>
+      </c>
+      <c r="F29">
+        <f>E29*$J$3</f>
+        <v/>
+      </c>
+      <c r="G29">
+        <f>IF(F29=0,"",ROUND(D29/(F29/30),0))</f>
+        <v/>
+      </c>
+      <c r="H29">
+        <f>MAX(0,ROUND(F29*$J$2-D29,0))</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>H29*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>COSRX</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>207481251</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>COSRX - Advanced Snail 96 Mucin Power Essence [100ml] /</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>38</v>
+      </c>
+      <c r="E30" t="n">
+        <v>46</v>
+      </c>
+      <c r="F30">
+        <f>E30*$J$3</f>
+        <v/>
+      </c>
+      <c r="G30">
+        <f>IF(F30=0,"",ROUND(D30/(F30/30),0))</f>
+        <v/>
+      </c>
+      <c r="H30">
+        <f>MAX(0,ROUND(F30*$J$2-D30,0))</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>H30*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>437797551</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ROUND LAB VITA NIACINAMIDE DARK SPOT SERUM 30ml - Сывор</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>62</v>
+      </c>
+      <c r="E31" t="n">
+        <v>40</v>
+      </c>
+      <c r="F31">
+        <f>E31*$J$3</f>
+        <v/>
+      </c>
+      <c r="G31">
+        <f>IF(F31=0,"",ROUND(D31/(F31/30),0))</f>
+        <v/>
+      </c>
+      <c r="H31">
+        <f>MAX(0,ROUND(F31*$J$2-D31,0))</f>
+        <v/>
+      </c>
+      <c r="I31">
+        <f>H31*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>608837066</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml]</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>122</v>
+      </c>
+      <c r="E32" t="n">
+        <v>39</v>
+      </c>
+      <c r="F32">
+        <f>E32*$J$3</f>
+        <v/>
+      </c>
+      <c r="G32">
+        <f>IF(F32=0,"",ROUND(D32/(F32/30),0))</f>
+        <v/>
+      </c>
+      <c r="H32">
+        <f>MAX(0,ROUND(F32*$J$2-D32,0))</f>
+        <v/>
+      </c>
+      <c r="I32">
+        <f>H32*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>611747838</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ENOUGH - Collagen Moisture Foundation [Tone 23] / Тонал</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>90</v>
+      </c>
+      <c r="E33" t="n">
+        <v>34</v>
+      </c>
+      <c r="F33">
+        <f>E33*$J$3</f>
+        <v/>
+      </c>
+      <c r="G33">
+        <f>IF(F33=0,"",ROUND(D33/(F33/30),0))</f>
+        <v/>
+      </c>
+      <c r="H33">
+        <f>MAX(0,ROUND(F33*$J$2-D33,0))</f>
+        <v/>
+      </c>
+      <c r="I33">
+        <f>H33*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>212753217</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>JIGOTT - Collagen Healing Cream [100ml] / Крем для лица</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>133</v>
+      </c>
+      <c r="E34" t="n">
+        <v>31</v>
+      </c>
+      <c r="F34">
+        <f>E34*$J$3</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>IF(F34=0,"",ROUND(D34/(F34/30),0))</f>
+        <v/>
+      </c>
+      <c r="H34">
+        <f>MAX(0,ROUND(F34*$J$2-D34,0))</f>
+        <v/>
+      </c>
+      <c r="I34">
+        <f>H34*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>437776835</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка дл</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>103</v>
+      </c>
+      <c r="E35" t="n">
+        <v>31</v>
+      </c>
+      <c r="F35">
+        <f>E35*$J$3</f>
+        <v/>
+      </c>
+      <c r="G35">
+        <f>IF(F35=0,"",ROUND(D35/(F35/30),0))</f>
+        <v/>
+      </c>
+      <c r="H35">
+        <f>MAX(0,ROUND(F35*$J$2-D35,0))</f>
+        <v/>
+      </c>
+      <c r="I35">
+        <f>H35*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>608624295</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml]</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>143</v>
+      </c>
+      <c r="E36" t="n">
+        <v>30</v>
+      </c>
+      <c r="F36">
+        <f>E36*$J$3</f>
+        <v/>
+      </c>
+      <c r="G36">
+        <f>IF(F36=0,"",ROUND(D36/(F36/30),0))</f>
+        <v/>
+      </c>
+      <c r="H36">
+        <f>MAX(0,ROUND(F36*$J$2-D36,0))</f>
+        <v/>
+      </c>
+      <c r="I36">
+        <f>H36*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>DEOPROCE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>214304883</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DEOPROCE - SNAIL RECOVERY CREAM [100g] / Крем восстанав</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>57</v>
+      </c>
+      <c r="E37" t="n">
+        <v>22</v>
+      </c>
+      <c r="F37">
+        <f>E37*$J$3</f>
+        <v/>
+      </c>
+      <c r="G37">
+        <f>IF(F37=0,"",ROUND(D37/(F37/30),0))</f>
+        <v/>
+      </c>
+      <c r="H37">
+        <f>MAX(0,ROUND(F37*$J$2-D37,0))</f>
+        <v/>
+      </c>
+      <c r="I37">
+        <f>H37*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TheOrdinary</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>214312385</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>THE ORDINARY - Argireline Solution 10% [30ml] / Сыворот</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>127</v>
+      </c>
+      <c r="E38" t="n">
+        <v>22</v>
+      </c>
+      <c r="F38">
+        <f>E38*$J$3</f>
+        <v/>
+      </c>
+      <c r="G38">
+        <f>IF(F38=0,"",ROUND(D38/(F38/30),0))</f>
+        <v/>
+      </c>
+      <c r="H38">
+        <f>MAX(0,ROUND(F38*$J$2-D38,0))</f>
+        <v/>
+      </c>
+      <c r="I38">
+        <f>H38*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>180992464</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>126</v>
+      </c>
+      <c r="E39" t="n">
+        <v>20</v>
+      </c>
+      <c r="F39">
+        <f>E39*$J$3</f>
+        <v/>
+      </c>
+      <c r="G39">
+        <f>IF(F39=0,"",ROUND(D39/(F39/30),0))</f>
+        <v/>
+      </c>
+      <c r="H39">
+        <f>MAX(0,ROUND(F39*$J$2-D39,0))</f>
+        <v/>
+      </c>
+      <c r="I39">
+        <f>H39*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>LEBELAGE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>207818642</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>LEBELAGE - Dr. Hyaluronic Derma Eye Cream [40ml] / Крем</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>39</v>
+      </c>
+      <c r="E40" t="n">
+        <v>19</v>
+      </c>
+      <c r="F40">
+        <f>E40*$J$3</f>
+        <v/>
+      </c>
+      <c r="G40">
+        <f>IF(F40=0,"",ROUND(D40/(F40/30),0))</f>
+        <v/>
+      </c>
+      <c r="H40">
+        <f>MAX(0,ROUND(F40*$J$2-D40,0))</f>
+        <v/>
+      </c>
+      <c r="I40">
+        <f>H40*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ISNTREE</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>207818000</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ISNTREE - Chestnut AHA 8% Clear Essence Sample [20ml] /</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>60</v>
+      </c>
+      <c r="E41" t="n">
+        <v>15</v>
+      </c>
+      <c r="F41">
+        <f>E41*$J$3</f>
+        <v/>
+      </c>
+      <c r="G41">
+        <f>IF(F41=0,"",ROUND(D41/(F41/30),0))</f>
+        <v/>
+      </c>
+      <c r="H41">
+        <f>MAX(0,ROUND(F41*$J$2-D41,0))</f>
+        <v/>
+      </c>
+      <c r="I41">
+        <f>H41*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>437850261</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ROUND LAB SOYBEAN CLEANSING OIL_200ml - Гидрофильное ма</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>30</v>
+      </c>
+      <c r="E42" t="n">
+        <v>14</v>
+      </c>
+      <c r="F42">
+        <f>E42*$J$3</f>
+        <v/>
+      </c>
+      <c r="G42">
+        <f>IF(F42=0,"",ROUND(D42/(F42/30),0))</f>
+        <v/>
+      </c>
+      <c r="H42">
+        <f>MAX(0,ROUND(F42*$J$2-D42,0))</f>
+        <v/>
+      </c>
+      <c r="I42">
+        <f>H42*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ENOUGH</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>611744611</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>8</v>
+      </c>
+      <c r="F43">
+        <f>E43*$J$3</f>
+        <v/>
+      </c>
+      <c r="G43">
+        <f>IF(F43=0,"",ROUND(D43/(F43/30),0))</f>
+        <v/>
+      </c>
+      <c r="H43">
+        <f>MAX(0,ROUND(F43*$J$2-D43,0))</f>
+        <v/>
+      </c>
+      <c r="I43">
+        <f>H43*$J$4/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="H44" s="1">
+        <f>SUM(H3:H43)</f>
+        <v/>
+      </c>
+      <c r="I44" s="1">
+        <f>SUM(I3:I43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Проверка веса, т</t>
+        </is>
+      </c>
+      <c r="D46">
+        <f>I44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Проверка штук</t>
+        </is>
+      </c>
+      <c r="D47">
+        <f>H44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>FarmStay исключён. Контейнер = позиции с покрытием &lt;150 дней, докуп до 6 мес спроса 2 магазинов.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G3:G43">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>90</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/coverage/pokrytie_po_brendam_2026-06-30.xlsx
+++ b/outputs/coverage/pokrytie_po_brendam_2026-06-30.xlsx
@@ -78,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -89,6 +89,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7410,120 +7413,163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Транзит, мес</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="n">
-        <v>2</v>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Бренд</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Баркод</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>кол-во</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>сумма</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>в коробе</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>Объем короба</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>Вес короба кг</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>Коробок в заказ</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>Объем</t>
+        </is>
+      </c>
+      <c r="L1" s="6" t="inlineStr">
+        <is>
+          <t>Вес кг</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Бренд</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Артикул</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Название</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Итого сейчас</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Продажи/мес</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Спрос 2маг/мес</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Хватит дней</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>В контейнер, шт</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>Вес, т</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>6</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CELIMAX</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыво</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8809700320805</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1266</v>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2">
+        <f>D2*E2</f>
+        <v/>
+      </c>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2">
+        <f>IF(G2="","",ROUNDUP(D2/G2,0))</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>IF(J2="","",J2*H2)</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>IF(J2="","",J2*I2)</f>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CELIMAX</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>551465879</t>
+          <t>ENOUGH - Collagen 3in1 Sun Cream SPF50 PA+++ [50ml] / отбели</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]</t>
+          <t>8809755462130</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4856</v>
-      </c>
-      <c r="E3" t="n">
-        <v>618</v>
-      </c>
+        <v>5018</v>
+      </c>
+      <c r="E3" s="2" t="n"/>
       <c r="F3">
-        <f>E3*$J$3</f>
-        <v/>
-      </c>
-      <c r="G3">
-        <f>IF(F3=0,"",ROUND(D3/(F3/30),0))</f>
-        <v/>
-      </c>
-      <c r="H3">
-        <f>MAX(0,ROUND(F3*$J$2-D3,0))</f>
-        <v/>
-      </c>
-      <c r="I3" s="1">
-        <f>H3*$J$4/1000</f>
-        <v/>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>1.65</v>
+        <f>D3*E3</f>
+        <v/>
+      </c>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3">
+        <f>IF(G3="","",ROUNDUP(D3/G3,0))</f>
+        <v/>
+      </c>
+      <c r="K3">
+        <f>IF(J3="","",J3*H3)</f>
+        <v/>
+      </c>
+      <c r="L3">
+        <f>IF(J3="","",J3*I3)</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -7534,355 +7580,355 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>238358954</t>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13] / Тональны</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen 3in1 Sun Cream SPF50 PA+++ [50ml] / о</t>
+          <t>8809474498809</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>318</v>
-      </c>
-      <c r="E4" t="n">
-        <v>539</v>
-      </c>
+        <v>1990</v>
+      </c>
+      <c r="E4" s="2" t="n"/>
       <c r="F4">
-        <f>E4*$J$3</f>
-        <v/>
-      </c>
-      <c r="G4">
-        <f>IF(F4=0,"",ROUND(D4/(F4/30),0))</f>
-        <v/>
-      </c>
-      <c r="H4">
-        <f>MAX(0,ROUND(F4*$J$2-D4,0))</f>
-        <v/>
-      </c>
-      <c r="I4" s="1">
-        <f>H4*$J$4/1000</f>
-        <v/>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0.35</v>
+        <f>D4*E4</f>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4">
+        <f>IF(G4="","",ROUNDUP(D4/G4,0))</f>
+        <v/>
+      </c>
+      <c r="K4">
+        <f>IF(J4="","",J4*H4)</f>
+        <v/>
+      </c>
+      <c r="L4">
+        <f>IF(J4="","",J4*I4)</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>207796789</t>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыво</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13] / Тон</t>
+          <t>8809730952014</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1036</v>
-      </c>
-      <c r="E5" t="n">
-        <v>306</v>
-      </c>
+        <v>1204</v>
+      </c>
+      <c r="E5" s="2" t="n"/>
       <c r="F5">
-        <f>E5*$J$3</f>
-        <v/>
-      </c>
-      <c r="G5">
-        <f>IF(F5=0,"",ROUND(D5/(F5/30),0))</f>
-        <v/>
-      </c>
-      <c r="H5">
-        <f>MAX(0,ROUND(F5*$J$2-D5,0))</f>
-        <v/>
-      </c>
-      <c r="I5" s="1">
-        <f>H5*$J$4/1000</f>
-        <v/>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>26</v>
+        <f>D5*E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5">
+        <f>IF(G5="","",ROUNDUP(D5/G5,0))</f>
+        <v/>
+      </c>
+      <c r="K5">
+        <f>IF(J5="","",J5*H5)</f>
+        <v/>
+      </c>
+      <c r="L5">
+        <f>IF(J5="","",J5*I5)</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>198156472</t>
+          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажн</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая</t>
+          <t>8809210036517</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1142</v>
-      </c>
-      <c r="E6" t="n">
-        <v>237</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="E6" s="2" t="n"/>
       <c r="F6">
-        <f>E6*$J$3</f>
-        <v/>
-      </c>
-      <c r="G6">
-        <f>IF(F6=0,"",ROUND(D6/(F6/30),0))</f>
-        <v/>
-      </c>
-      <c r="H6">
-        <f>MAX(0,ROUND(F6*$J$2-D6,0))</f>
-        <v/>
-      </c>
-      <c r="I6" s="1">
-        <f>H6*$J$4/1000</f>
-        <v/>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>120000</v>
+        <f>D6*E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6">
+        <f>IF(G6="","",ROUNDUP(D6/G6,0))</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>IF(J6="","",J6*H6)</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>IF(J6="","",J6*I6)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>207483179</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Ги</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица у</t>
+          <t>8809239801820</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1540</v>
-      </c>
-      <c r="E7" t="n">
-        <v>212</v>
-      </c>
+        <v>643</v>
+      </c>
+      <c r="E7" s="2" t="n"/>
       <c r="F7">
-        <f>E7*$J$3</f>
-        <v/>
-      </c>
-      <c r="G7">
-        <f>IF(F7=0,"",ROUND(D7/(F7/30),0))</f>
-        <v/>
-      </c>
-      <c r="H7">
-        <f>MAX(0,ROUND(F7*$J$2-D7,0))</f>
-        <v/>
-      </c>
-      <c r="I7">
-        <f>H7*$J$4/1000</f>
+        <f>D7*E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7">
+        <f>IF(G7="","",ROUNDUP(D7/G7,0))</f>
+        <v/>
+      </c>
+      <c r="K7">
+        <f>IF(J7="","",J7*H7)</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>IF(J7="","",J7*I7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>151175880</t>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21] / Тональны</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea]</t>
+          <t>8809474498816</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1185</v>
-      </c>
-      <c r="E8" t="n">
-        <v>185</v>
-      </c>
+        <v>1048</v>
+      </c>
+      <c r="E8" s="2" t="n"/>
       <c r="F8">
-        <f>E8*$J$3</f>
-        <v/>
-      </c>
-      <c r="G8">
-        <f>IF(F8=0,"",ROUND(D8/(F8/30),0))</f>
-        <v/>
-      </c>
-      <c r="H8">
-        <f>MAX(0,ROUND(F8*$J$2-D8,0))</f>
-        <v/>
-      </c>
-      <c r="I8">
-        <f>H8*$J$4/1000</f>
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8">
+        <f>IF(G8="","",ROUNDUP(D8/G8,0))</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IF(J8="","",J8*H8)</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>IF(J8="","",J8*I8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>ELIZAVECCA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>207796898</t>
+          <t>ELIZAVECCA - Aqua Hyaluronic Acid Water Drop Cream / Увлажня</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21] / Тон</t>
+          <t>8809418750505</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>684</v>
-      </c>
-      <c r="E9" t="n">
-        <v>175</v>
-      </c>
+        <v>1651</v>
+      </c>
+      <c r="E9" s="2" t="n"/>
       <c r="F9">
-        <f>E9*$J$3</f>
-        <v/>
-      </c>
-      <c r="G9">
-        <f>IF(F9=0,"",ROUND(D9/(F9/30),0))</f>
-        <v/>
-      </c>
-      <c r="H9">
-        <f>MAX(0,ROUND(F9*$J$2-D9,0))</f>
-        <v/>
-      </c>
-      <c r="I9">
-        <f>H9*$J$4/1000</f>
+        <f>D9*E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9">
+        <f>IF(G9="","",ROUNDUP(D9/G9,0))</f>
+        <v/>
+      </c>
+      <c r="K9">
+        <f>IF(J9="","",J9*H9)</f>
+        <v/>
+      </c>
+      <c r="L9">
+        <f>IF(J9="","",J9*I9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ELIZAVECCA</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>207796563</t>
+          <t>ENOUGH - Premium 8 Peptide Full Cover Perfect Foundation [To</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - Aqua Hyaluronic Acid Water Drop Cream / Ув</t>
+          <t>8809605870979</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
-      </c>
-      <c r="E10" t="n">
-        <v>171</v>
-      </c>
+        <v>955</v>
+      </c>
+      <c r="E10" s="2" t="n"/>
       <c r="F10">
-        <f>E10*$J$3</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>IF(F10=0,"",ROUND(D10/(F10/30),0))</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>MAX(0,ROUND(F10*$J$2-D10,0))</f>
-        <v/>
-      </c>
-      <c r="I10">
-        <f>H10*$J$4/1000</f>
+        <f>D10*E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10">
+        <f>IF(G10="","",ROUNDUP(D10/G10,0))</f>
+        <v/>
+      </c>
+      <c r="K10">
+        <f>IF(J10="","",J10*H10)</f>
+        <v/>
+      </c>
+      <c r="L10">
+        <f>IF(J10="","",J10*I10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>170198337</t>
+          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлажда</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ENOUGH - Premium 8 Peptide Full Cover Perfect Foundatio</t>
+          <t>8809508850443</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>632</v>
-      </c>
-      <c r="E11" t="n">
-        <v>160</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="E11" s="2" t="n"/>
       <c r="F11">
-        <f>E11*$J$3</f>
-        <v/>
-      </c>
-      <c r="G11">
-        <f>IF(F11=0,"",ROUND(D11/(F11/30),0))</f>
-        <v/>
-      </c>
-      <c r="H11">
-        <f>MAX(0,ROUND(F11*$J$2-D11,0))</f>
-        <v/>
-      </c>
-      <c r="I11">
-        <f>H11*$J$4/1000</f>
+        <f>D11*E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11">
+        <f>IF(G11="","",ROUNDUP(D11/G11,0))</f>
+        <v/>
+      </c>
+      <c r="K11">
+        <f>IF(J11="","",J11*H11)</f>
+        <v/>
+      </c>
+      <c r="L11">
+        <f>IF(J11="","",J11*I11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>226115324</t>
+          <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundation [</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Ох</t>
+          <t>8809605871938</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1197</v>
-      </c>
-      <c r="E12" t="n">
-        <v>153</v>
-      </c>
+        <v>749</v>
+      </c>
+      <c r="E12" s="2" t="n"/>
       <c r="F12">
-        <f>E12*$J$3</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>IF(F12=0,"",ROUND(D12/(F12/30),0))</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>MAX(0,ROUND(F12*$J$2-D12,0))</f>
-        <v/>
-      </c>
-      <c r="I12">
-        <f>H12*$J$4/1000</f>
+        <f>D12*E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12">
+        <f>IF(G12="","",ROUNDUP(D12/G12,0))</f>
+        <v/>
+      </c>
+      <c r="K12">
+        <f>IF(J12="","",J12*H12)</f>
+        <v/>
+      </c>
+      <c r="L12">
+        <f>IF(J12="","",J12*I12)</f>
         <v/>
       </c>
     </row>
@@ -7894,34 +7940,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>170198180</t>
+          <t>ENOUGH - Premium Ultra X10 Cover Up Collagen Foundation [Ton</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundat</t>
+          <t>8809605870993</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>627</v>
-      </c>
-      <c r="E13" t="n">
-        <v>139</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="E13" s="2" t="n"/>
       <c r="F13">
-        <f>E13*$J$3</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>IF(F13=0,"",ROUND(D13/(F13/30),0))</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>MAX(0,ROUND(F13*$J$2-D13,0))</f>
-        <v/>
-      </c>
-      <c r="I13">
-        <f>H13*$J$4/1000</f>
+        <f>D13*E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13">
+        <f>IF(G13="","",ROUNDUP(D13/G13,0))</f>
+        <v/>
+      </c>
+      <c r="K13">
+        <f>IF(J13="","",J13*H13)</f>
+        <v/>
+      </c>
+      <c r="L13">
+        <f>IF(J13="","",J13*I13)</f>
         <v/>
       </c>
     </row>
@@ -7933,112 +7980,115 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>170198835</t>
+          <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundation [</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ENOUGH - Premium Ultra X10 Cover Up Collagen Foundation</t>
+          <t>8809605871945</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E14" t="n">
-        <v>135</v>
-      </c>
+        <v>698</v>
+      </c>
+      <c r="E14" s="2" t="n"/>
       <c r="F14">
-        <f>E14*$J$3</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>IF(F14=0,"",ROUND(D14/(F14/30),0))</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>MAX(0,ROUND(F14*$J$2-D14,0))</f>
-        <v/>
-      </c>
-      <c r="I14">
-        <f>H14*$J$4/1000</f>
+        <f>D14*E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14">
+        <f>IF(G14="","",ROUNDUP(D14/G14,0))</f>
+        <v/>
+      </c>
+      <c r="K14">
+        <f>IF(J14="","",J14*H14)</f>
+        <v/>
+      </c>
+      <c r="L14">
+        <f>IF(J14="","",J14*I14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>ELIZAVECCA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>170198109</t>
+          <t>ELIZAVECCA - Natural 90% Olive Cleansing Oil / Очищающее гид</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundat</t>
+          <t>8809071365504</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>540</v>
-      </c>
-      <c r="E15" t="n">
-        <v>125</v>
-      </c>
+        <v>1203</v>
+      </c>
+      <c r="E15" s="2" t="n"/>
       <c r="F15">
-        <f>E15*$J$3</f>
-        <v/>
-      </c>
-      <c r="G15">
-        <f>IF(F15=0,"",ROUND(D15/(F15/30),0))</f>
-        <v/>
-      </c>
-      <c r="H15">
-        <f>MAX(0,ROUND(F15*$J$2-D15,0))</f>
-        <v/>
-      </c>
-      <c r="I15">
-        <f>H15*$J$4/1000</f>
+        <f>D15*E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15">
+        <f>IF(G15="","",ROUNDUP(D15/G15,0))</f>
+        <v/>
+      </c>
+      <c r="K15">
+        <f>IF(J15="","",J15*H15)</f>
+        <v/>
+      </c>
+      <c r="L15">
+        <f>IF(J15="","",J15*I15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ELIZAVECCA</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>207796439</t>
+          <t>MANYO - Bifida Biome Ampoule Toner [400ml] / Ампульный укреп</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - Natural 90% Olive Cleansing Oil / Очищающе</t>
+          <t>8809657114137</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" t="n">
-        <v>122</v>
-      </c>
+        <v>1111</v>
+      </c>
+      <c r="E16" s="2" t="n"/>
       <c r="F16">
-        <f>E16*$J$3</f>
-        <v/>
-      </c>
-      <c r="G16">
-        <f>IF(F16=0,"",ROUND(D16/(F16/30),0))</f>
-        <v/>
-      </c>
-      <c r="H16">
-        <f>MAX(0,ROUND(F16*$J$2-D16,0))</f>
-        <v/>
-      </c>
-      <c r="I16">
-        <f>H16*$J$4/1000</f>
+        <f>D16*E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16">
+        <f>IF(G16="","",ROUNDUP(D16/G16,0))</f>
+        <v/>
+      </c>
+      <c r="K16">
+        <f>IF(J16="","",J16*H16)</f>
+        <v/>
+      </c>
+      <c r="L16">
+        <f>IF(J16="","",J16*I16)</f>
         <v/>
       </c>
     </row>
@@ -8050,736 +8100,759 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>205054338</t>
+          <t xml:space="preserve">MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANYO - Bifida Biome Ampoule Toner [400ml] / Ампульный </t>
+          <t>8809082392292</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>112</v>
-      </c>
+        <v>678</v>
+      </c>
+      <c r="E17" s="2" t="n"/>
       <c r="F17">
-        <f>E17*$J$3</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>IF(F17=0,"",ROUND(D17/(F17/30),0))</f>
-        <v/>
-      </c>
-      <c r="H17">
-        <f>MAX(0,ROUND(F17*$J$2-D17,0))</f>
-        <v/>
-      </c>
-      <c r="I17">
-        <f>H17*$J$4/1000</f>
+        <f>D17*E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17">
+        <f>IF(G17="","",ROUNDUP(D17/G17,0))</f>
+        <v/>
+      </c>
+      <c r="K17">
+        <f>IF(J17="","",J17*H17)</f>
+        <v/>
+      </c>
+      <c r="L17">
+        <f>IF(J17="","",J17*I17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MANYO</t>
+          <t>ELIZAVECCA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>198156698</t>
+          <t>ELIZAVECCA - Hell pore clean up aha fruit toner [ 200ml] / П</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло</t>
+          <t>8809339907910</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>368</v>
-      </c>
-      <c r="E18" t="n">
-        <v>106</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="E18" s="2" t="n"/>
       <c r="F18">
-        <f>E18*$J$3</f>
-        <v/>
-      </c>
-      <c r="G18">
-        <f>IF(F18=0,"",ROUND(D18/(F18/30),0))</f>
-        <v/>
-      </c>
-      <c r="H18">
-        <f>MAX(0,ROUND(F18*$J$2-D18,0))</f>
-        <v/>
-      </c>
-      <c r="I18">
-        <f>H18*$J$4/1000</f>
+        <f>D18*E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18">
+        <f>IF(G18="","",ROUNDUP(D18/G18,0))</f>
+        <v/>
+      </c>
+      <c r="K18">
+        <f>IF(J18="","",J18*H18)</f>
+        <v/>
+      </c>
+      <c r="L18">
+        <f>IF(J18="","",J18*I18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ELIZAVECCA</t>
+          <t>DEOPROCE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>206057411</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA - Hell pore clean up aha fruit toner [ 200ml</t>
-        </is>
-      </c>
+          <t>DEOPROCE SHAMPOO+BALSAM - BLACK GARLIC[2000ml]</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>458</v>
-      </c>
-      <c r="E19" t="n">
-        <v>105</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="E19" s="2" t="n"/>
       <c r="F19">
-        <f>E19*$J$3</f>
-        <v/>
-      </c>
-      <c r="G19">
-        <f>IF(F19=0,"",ROUND(D19/(F19/30),0))</f>
-        <v/>
-      </c>
-      <c r="H19">
-        <f>MAX(0,ROUND(F19*$J$2-D19,0))</f>
-        <v/>
-      </c>
-      <c r="I19">
-        <f>H19*$J$4/1000</f>
+        <f>D19*E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19">
+        <f>IF(G19="","",ROUNDUP(D19/G19,0))</f>
+        <v/>
+      </c>
+      <c r="K19">
+        <f>IF(J19="","",J19*H19)</f>
+        <v/>
+      </c>
+      <c r="L19">
+        <f>IF(J19="","",J19*I19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DEOPROCE</t>
+          <t>ELIZAVECCA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>214305722</t>
+          <t>ELIZAVECCA - 24K Gold Snail Cleansing Foam [180ml] / Золотая</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO+BALSAM - BLACK GARLIC[2000ml]</t>
+          <t>8809418750338</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>570</v>
-      </c>
-      <c r="E20" t="n">
-        <v>95</v>
-      </c>
+        <v>896</v>
+      </c>
+      <c r="E20" s="2" t="n"/>
       <c r="F20">
-        <f>E20*$J$3</f>
-        <v/>
-      </c>
-      <c r="G20">
-        <f>IF(F20=0,"",ROUND(D20/(F20/30),0))</f>
-        <v/>
-      </c>
-      <c r="H20">
-        <f>MAX(0,ROUND(F20*$J$2-D20,0))</f>
-        <v/>
-      </c>
-      <c r="I20">
-        <f>H20*$J$4/1000</f>
+        <f>D20*E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20">
+        <f>IF(G20="","",ROUNDUP(D20/G20,0))</f>
+        <v/>
+      </c>
+      <c r="K20">
+        <f>IF(J20="","",J20*H20)</f>
+        <v/>
+      </c>
+      <c r="L20">
+        <f>IF(J20="","",J20*I20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ELIZAVECCA</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>190159348</t>
+          <t>ENOUGH - Premium Ultra X10 Cover Up Collagen Foundation [Ton</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - 24K Gold Snail Cleansing Foam [180ml] / Зо</t>
+          <t>8809605871006</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45</v>
+        <v>610</v>
       </c>
       <c r="E21" t="n">
-        <v>95</v>
+        <v>3880</v>
       </c>
       <c r="F21">
-        <f>E21*$J$3</f>
-        <v/>
-      </c>
-      <c r="G21">
-        <f>IF(F21=0,"",ROUND(D21/(F21/30),0))</f>
-        <v/>
-      </c>
-      <c r="H21">
-        <f>MAX(0,ROUND(F21*$J$2-D21,0))</f>
-        <v/>
-      </c>
-      <c r="I21">
-        <f>H21*$J$4/1000</f>
+        <f>D21*E21</f>
+        <v/>
+      </c>
+      <c r="G21" t="n">
+        <v>100</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0314</v>
+      </c>
+      <c r="I21" t="n">
+        <v>15</v>
+      </c>
+      <c r="J21">
+        <f>IF(G21="","",ROUNDUP(D21/G21,0))</f>
+        <v/>
+      </c>
+      <c r="K21">
+        <f>IF(J21="","",J21*H21)</f>
+        <v/>
+      </c>
+      <c r="L21">
+        <f>IF(J21="","",J21*I21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>170198876</t>
+          <t xml:space="preserve">PETITFEE - Chamomile Lightening Hydrogel Mask Pack [5pcs] / </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ENOUGH - Premium Ultra X10 Cover Up Collagen Foundation</t>
+          <t>8809508850436</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>278</v>
-      </c>
-      <c r="E22" t="n">
-        <v>90</v>
-      </c>
+        <v>745</v>
+      </c>
+      <c r="E22" s="2" t="n"/>
       <c r="F22">
-        <f>E22*$J$3</f>
-        <v/>
-      </c>
-      <c r="G22">
-        <f>IF(F22=0,"",ROUND(D22/(F22/30),0))</f>
-        <v/>
-      </c>
-      <c r="H22">
-        <f>MAX(0,ROUND(F22*$J$2-D22,0))</f>
-        <v/>
-      </c>
-      <c r="I22">
-        <f>H22*$J$4/1000</f>
+        <f>D22*E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22">
+        <f>IF(G22="","",ROUNDUP(D22/G22,0))</f>
+        <v/>
+      </c>
+      <c r="K22">
+        <f>IF(J22="","",J22*H22)</f>
+        <v/>
+      </c>
+      <c r="L22">
+        <f>IF(J22="","",J22*I22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>EKEL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>226117746</t>
+          <t>EKEL - Ampule Сream Сollagen [70ml] / Крем для лица ампульны</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PETITFEE - Chamomile Lightening Hydrogel Mask Pack [5pc</t>
+          <t>8809242276820</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>129</v>
-      </c>
-      <c r="E23" t="n">
-        <v>88</v>
-      </c>
+        <v>501</v>
+      </c>
+      <c r="E23" s="2" t="n"/>
       <c r="F23">
-        <f>E23*$J$3</f>
-        <v/>
-      </c>
-      <c r="G23">
-        <f>IF(F23=0,"",ROUND(D23/(F23/30),0))</f>
-        <v/>
-      </c>
-      <c r="H23">
-        <f>MAX(0,ROUND(F23*$J$2-D23,0))</f>
-        <v/>
-      </c>
-      <c r="I23">
-        <f>H23*$J$4/1000</f>
+        <f>D23*E23</f>
+        <v/>
+      </c>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23">
+        <f>IF(G23="","",ROUNDUP(D23/G23,0))</f>
+        <v/>
+      </c>
+      <c r="K23">
+        <f>IF(J23="","",J23*H23)</f>
+        <v/>
+      </c>
+      <c r="L23">
+        <f>IF(J23="","",J23*I23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EKEL</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>208202076</t>
+          <t>ROUND LAB SOYBEAN PANTHENOL CREAM_80ml - Крем для лица с чёр</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EKEL - Ampule Сream Сollagen [70ml] / Крем для лица амп</t>
+          <t>8809875907337</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>324</v>
-      </c>
-      <c r="E24" t="n">
-        <v>83</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="E24" s="2" t="n"/>
       <c r="F24">
-        <f>E24*$J$3</f>
-        <v/>
-      </c>
-      <c r="G24">
-        <f>IF(F24=0,"",ROUND(D24/(F24/30),0))</f>
-        <v/>
-      </c>
-      <c r="H24">
-        <f>MAX(0,ROUND(F24*$J$2-D24,0))</f>
-        <v/>
-      </c>
-      <c r="I24">
-        <f>H24*$J$4/1000</f>
+        <f>D24*E24</f>
+        <v/>
+      </c>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24">
+        <f>IF(G24="","",ROUNDUP(D24/G24,0))</f>
+        <v/>
+      </c>
+      <c r="K24">
+        <f>IF(J24="","",J24*H24)</f>
+        <v/>
+      </c>
+      <c r="L24">
+        <f>IF(J24="","",J24*I24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>HEIMISH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>437254254</t>
+          <t>HEIMISH - All Clean Balm Mandarin [120ml] / Очищающий гидроф</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROUND LAB SOYBEAN PANTHENOL CREAM_80ml - Крем для лица </t>
+          <t>8809481761996</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>310</v>
-      </c>
-      <c r="E25" t="n">
-        <v>72</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="E25" s="2" t="n"/>
       <c r="F25">
-        <f>E25*$J$3</f>
-        <v/>
-      </c>
-      <c r="G25">
-        <f>IF(F25=0,"",ROUND(D25/(F25/30),0))</f>
-        <v/>
-      </c>
-      <c r="H25">
-        <f>MAX(0,ROUND(F25*$J$2-D25,0))</f>
-        <v/>
-      </c>
-      <c r="I25">
-        <f>H25*$J$4/1000</f>
+        <f>D25*E25</f>
+        <v/>
+      </c>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
+      <c r="J25">
+        <f>IF(G25="","",ROUNDUP(D25/G25,0))</f>
+        <v/>
+      </c>
+      <c r="K25">
+        <f>IF(J25="","",J25*H25)</f>
+        <v/>
+      </c>
+      <c r="L25">
+        <f>IF(J25="","",J25*I25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HEIMISH</t>
+          <t>ETUDEHOUSE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>207465786</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [24*7ml] / Очищающий</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HEIMISH - All Clean Balm Mandarin [120ml] / Очищающий г</t>
+          <t>8809820692707</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>108</v>
-      </c>
-      <c r="E26" t="n">
-        <v>68</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="E26" s="2" t="n"/>
       <c r="F26">
-        <f>E26*$J$3</f>
-        <v/>
-      </c>
-      <c r="G26">
-        <f>IF(F26=0,"",ROUND(D26/(F26/30),0))</f>
-        <v/>
-      </c>
-      <c r="H26">
-        <f>MAX(0,ROUND(F26*$J$2-D26,0))</f>
-        <v/>
-      </c>
-      <c r="I26">
-        <f>H26*$J$4/1000</f>
+        <f>D26*E26</f>
+        <v/>
+      </c>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26">
+        <f>IF(G26="","",ROUNDUP(D26/G26,0))</f>
+        <v/>
+      </c>
+      <c r="K26">
+        <f>IF(J26="","",J26*H26)</f>
+        <v/>
+      </c>
+      <c r="L26">
+        <f>IF(J26="","",J26*I26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ETUDEHOUSE</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>154160085</t>
+          <t xml:space="preserve">PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea] / </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [24*7ml] / Очищ</t>
+          <t>8809508850412</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>309</v>
-      </c>
-      <c r="E27" t="n">
-        <v>65</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="E27" s="2" t="n"/>
       <c r="F27">
-        <f>E27*$J$3</f>
-        <v/>
-      </c>
-      <c r="G27">
-        <f>IF(F27=0,"",ROUND(D27/(F27/30),0))</f>
-        <v/>
-      </c>
-      <c r="H27">
-        <f>MAX(0,ROUND(F27*$J$2-D27,0))</f>
-        <v/>
-      </c>
-      <c r="I27">
-        <f>H27*$J$4/1000</f>
+        <f>D27*E27</f>
+        <v/>
+      </c>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27">
+        <f>IF(G27="","",ROUNDUP(D27/G27,0))</f>
+        <v/>
+      </c>
+      <c r="K27">
+        <f>IF(J27="","",J27*H27)</f>
+        <v/>
+      </c>
+      <c r="L27">
+        <f>IF(J27="","",J27*I27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>ETUDEHOUSE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>179611318</t>
+          <t xml:space="preserve">ETUDE - Baking Powder BB Deep Cleansing Foam [30ml] / Пенка </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60e</t>
+          <t>8809668028058</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>357</v>
-      </c>
-      <c r="E28" t="n">
-        <v>50</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="E28" s="2" t="n"/>
       <c r="F28">
-        <f>E28*$J$3</f>
-        <v/>
-      </c>
-      <c r="G28">
-        <f>IF(F28=0,"",ROUND(D28/(F28/30),0))</f>
-        <v/>
-      </c>
-      <c r="H28">
-        <f>MAX(0,ROUND(F28*$J$2-D28,0))</f>
-        <v/>
-      </c>
-      <c r="I28">
-        <f>H28*$J$4/1000</f>
+        <f>D28*E28</f>
+        <v/>
+      </c>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28">
+        <f>IF(G28="","",ROUNDUP(D28/G28,0))</f>
+        <v/>
+      </c>
+      <c r="K28">
+        <f>IF(J28="","",J28*H28)</f>
+        <v/>
+      </c>
+      <c r="L28">
+        <f>IF(J28="","",J28*I28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ETUDEHOUSE</t>
+          <t>COSRX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>154159632</t>
+          <t>COSRX - Advanced Snail 96 Mucin Power Essence [100ml] / Высо</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder BB Deep Cleansing Foam [30ml] / П</t>
+          <t>8809416470009</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>175</v>
-      </c>
-      <c r="E29" t="n">
-        <v>50</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="E29" s="2" t="n"/>
       <c r="F29">
-        <f>E29*$J$3</f>
-        <v/>
-      </c>
-      <c r="G29">
-        <f>IF(F29=0,"",ROUND(D29/(F29/30),0))</f>
-        <v/>
-      </c>
-      <c r="H29">
-        <f>MAX(0,ROUND(F29*$J$2-D29,0))</f>
-        <v/>
-      </c>
-      <c r="I29">
-        <f>H29*$J$4/1000</f>
+        <f>D29*E29</f>
+        <v/>
+      </c>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
+      <c r="J29">
+        <f>IF(G29="","",ROUNDUP(D29/G29,0))</f>
+        <v/>
+      </c>
+      <c r="K29">
+        <f>IF(J29="","",J29*H29)</f>
+        <v/>
+      </c>
+      <c r="L29">
+        <f>IF(J29="","",J29*I29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COSRX</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>207481251</t>
+          <t xml:space="preserve">ROUND LAB VITA NIACINAMIDE DARK SPOT SERUM 30ml - Сыворотка </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>COSRX - Advanced Snail 96 Mucin Power Essence [100ml] /</t>
+          <t>8809962540652</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>38</v>
-      </c>
-      <c r="E30" t="n">
-        <v>46</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="E30" s="2" t="n"/>
       <c r="F30">
-        <f>E30*$J$3</f>
-        <v/>
-      </c>
-      <c r="G30">
-        <f>IF(F30=0,"",ROUND(D30/(F30/30),0))</f>
-        <v/>
-      </c>
-      <c r="H30">
-        <f>MAX(0,ROUND(F30*$J$2-D30,0))</f>
-        <v/>
-      </c>
-      <c r="I30">
-        <f>H30*$J$4/1000</f>
+        <f>D30*E30</f>
+        <v/>
+      </c>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30">
+        <f>IF(G30="","",ROUNDUP(D30/G30,0))</f>
+        <v/>
+      </c>
+      <c r="K30">
+        <f>IF(J30="","",J30*H30)</f>
+        <v/>
+      </c>
+      <c r="L30">
+        <f>IF(J30="","",J30*I30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>DEOPROCE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>437797551</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml] мягк</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ROUND LAB VITA NIACINAMIDE DARK SPOT SERUM 30ml - Сывор</t>
+          <t>8809975191773</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
-      </c>
-      <c r="E31" t="n">
-        <v>40</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="E31" s="2" t="n"/>
       <c r="F31">
-        <f>E31*$J$3</f>
-        <v/>
-      </c>
-      <c r="G31">
-        <f>IF(F31=0,"",ROUND(D31/(F31/30),0))</f>
-        <v/>
-      </c>
-      <c r="H31">
-        <f>MAX(0,ROUND(F31*$J$2-D31,0))</f>
-        <v/>
-      </c>
-      <c r="I31">
-        <f>H31*$J$4/1000</f>
+        <f>D31*E31</f>
+        <v/>
+      </c>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="n"/>
+      <c r="J31">
+        <f>IF(G31="","",ROUNDUP(D31/G31,0))</f>
+        <v/>
+      </c>
+      <c r="K31">
+        <f>IF(J31="","",J31*H31)</f>
+        <v/>
+      </c>
+      <c r="L31">
+        <f>IF(J31="","",J31*I31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DEOPROCE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>608837066</t>
+          <t xml:space="preserve">ENOUGH - Collagen Moisture Foundation [Tone 23] / Тональный </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml]</t>
+          <t>8809280062386</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>122</v>
-      </c>
-      <c r="E32" t="n">
-        <v>39</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="E32" s="2" t="n"/>
       <c r="F32">
-        <f>E32*$J$3</f>
-        <v/>
-      </c>
-      <c r="G32">
-        <f>IF(F32=0,"",ROUND(D32/(F32/30),0))</f>
-        <v/>
-      </c>
-      <c r="H32">
-        <f>MAX(0,ROUND(F32*$J$2-D32,0))</f>
-        <v/>
-      </c>
-      <c r="I32">
-        <f>H32*$J$4/1000</f>
+        <f>D32*E32</f>
+        <v/>
+      </c>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32">
+        <f>IF(G32="","",ROUNDUP(D32/G32,0))</f>
+        <v/>
+      </c>
+      <c r="K32">
+        <f>IF(J32="","",J32*H32)</f>
+        <v/>
+      </c>
+      <c r="L32">
+        <f>IF(J32="","",J32*I32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>611747838</t>
+          <t>JIGOTT - Collagen Healing Cream [100ml] / Крем для лица с ко</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Foundation [Tone 23] / Тонал</t>
+          <t>8809210036524</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>90</v>
-      </c>
-      <c r="E33" t="n">
-        <v>34</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="E33" s="2" t="n"/>
       <c r="F33">
-        <f>E33*$J$3</f>
-        <v/>
-      </c>
-      <c r="G33">
-        <f>IF(F33=0,"",ROUND(D33/(F33/30),0))</f>
-        <v/>
-      </c>
-      <c r="H33">
-        <f>MAX(0,ROUND(F33*$J$2-D33,0))</f>
-        <v/>
-      </c>
-      <c r="I33">
-        <f>H33*$J$4/1000</f>
+        <f>D33*E33</f>
+        <v/>
+      </c>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
+      <c r="J33">
+        <f>IF(G33="","",ROUNDUP(D33/G33,0))</f>
+        <v/>
+      </c>
+      <c r="K33">
+        <f>IF(J33="","",J33*H33)</f>
+        <v/>
+      </c>
+      <c r="L33">
+        <f>IF(J33="","",J33*I33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>212753217</t>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жир</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JIGOTT - Collagen Healing Cream [100ml] / Крем для лица</t>
+          <t>8809783325667</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>133</v>
-      </c>
-      <c r="E34" t="n">
-        <v>31</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="E34" s="2" t="n"/>
       <c r="F34">
-        <f>E34*$J$3</f>
-        <v/>
-      </c>
-      <c r="G34">
-        <f>IF(F34=0,"",ROUND(D34/(F34/30),0))</f>
-        <v/>
-      </c>
-      <c r="H34">
-        <f>MAX(0,ROUND(F34*$J$2-D34,0))</f>
-        <v/>
-      </c>
-      <c r="I34">
-        <f>H34*$J$4/1000</f>
+        <f>D34*E34</f>
+        <v/>
+      </c>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34">
+        <f>IF(G34="","",ROUNDUP(D34/G34,0))</f>
+        <v/>
+      </c>
+      <c r="K34">
+        <f>IF(J34="","",J34*H34)</f>
+        <v/>
+      </c>
+      <c r="L34">
+        <f>IF(J34="","",J34*I34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>DEOPROCE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>437776835</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml] мягк</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка дл</t>
+          <t>8809975191766</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>103</v>
-      </c>
-      <c r="E35" t="n">
-        <v>31</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="E35" s="2" t="n"/>
       <c r="F35">
-        <f>E35*$J$3</f>
-        <v/>
-      </c>
-      <c r="G35">
-        <f>IF(F35=0,"",ROUND(D35/(F35/30),0))</f>
-        <v/>
-      </c>
-      <c r="H35">
-        <f>MAX(0,ROUND(F35*$J$2-D35,0))</f>
-        <v/>
-      </c>
-      <c r="I35">
-        <f>H35*$J$4/1000</f>
+        <f>D35*E35</f>
+        <v/>
+      </c>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35">
+        <f>IF(G35="","",ROUNDUP(D35/G35,0))</f>
+        <v/>
+      </c>
+      <c r="K35">
+        <f>IF(J35="","",J35*H35)</f>
+        <v/>
+      </c>
+      <c r="L35">
+        <f>IF(J35="","",J35*I35)</f>
         <v/>
       </c>
     </row>
@@ -8791,360 +8864,320 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>608624295</t>
+          <t>DEOPROCE - SNAIL RECOVERY CREAM [100g] / Крем восстанавливаю</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml]</t>
+          <t>8809240760659</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>143</v>
-      </c>
-      <c r="E36" t="n">
-        <v>30</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="E36" s="2" t="n"/>
       <c r="F36">
-        <f>E36*$J$3</f>
-        <v/>
-      </c>
-      <c r="G36">
-        <f>IF(F36=0,"",ROUND(D36/(F36/30),0))</f>
-        <v/>
-      </c>
-      <c r="H36">
-        <f>MAX(0,ROUND(F36*$J$2-D36,0))</f>
-        <v/>
-      </c>
-      <c r="I36">
-        <f>H36*$J$4/1000</f>
+        <f>D36*E36</f>
+        <v/>
+      </c>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36">
+        <f>IF(G36="","",ROUNDUP(D36/G36,0))</f>
+        <v/>
+      </c>
+      <c r="K36">
+        <f>IF(J36="","",J36*H36)</f>
+        <v/>
+      </c>
+      <c r="L36">
+        <f>IF(J36="","",J36*I36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DEOPROCE</t>
+          <t>TheOrdinary</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>214304883</t>
+          <t>THE ORDINARY - Argireline Solution 10% [30ml] / Сыворотка дл</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DEOPROCE - SNAIL RECOVERY CREAM [100g] / Крем восстанав</t>
+          <t>769915190946</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>57</v>
-      </c>
-      <c r="E37" t="n">
-        <v>22</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="E37" s="2" t="n"/>
       <c r="F37">
-        <f>E37*$J$3</f>
-        <v/>
-      </c>
-      <c r="G37">
-        <f>IF(F37=0,"",ROUND(D37/(F37/30),0))</f>
-        <v/>
-      </c>
-      <c r="H37">
-        <f>MAX(0,ROUND(F37*$J$2-D37,0))</f>
-        <v/>
-      </c>
-      <c r="I37">
-        <f>H37*$J$4/1000</f>
+        <f>D37*E37</f>
+        <v/>
+      </c>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37">
+        <f>IF(G37="","",ROUNDUP(D37/G37,0))</f>
+        <v/>
+      </c>
+      <c r="K37">
+        <f>IF(J37="","",J37*H37)</f>
+        <v/>
+      </c>
+      <c r="L37">
+        <f>IF(J37="","",J37*I37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TheOrdinary</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>214312385</t>
+          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Argireline Solution 10% [30ml] / Сыворот</t>
+          <t>8809508850801</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>127</v>
-      </c>
-      <c r="E38" t="n">
-        <v>22</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="E38" s="2" t="n"/>
       <c r="F38">
-        <f>E38*$J$3</f>
-        <v/>
-      </c>
-      <c r="G38">
-        <f>IF(F38=0,"",ROUND(D38/(F38/30),0))</f>
-        <v/>
-      </c>
-      <c r="H38">
-        <f>MAX(0,ROUND(F38*$J$2-D38,0))</f>
-        <v/>
-      </c>
-      <c r="I38">
-        <f>H38*$J$4/1000</f>
+        <f>D38*E38</f>
+        <v/>
+      </c>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38">
+        <f>IF(G38="","",ROUNDUP(D38/G38,0))</f>
+        <v/>
+      </c>
+      <c r="K38">
+        <f>IF(J38="","",J38*H38)</f>
+        <v/>
+      </c>
+      <c r="L38">
+        <f>IF(J38="","",J38*I38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>LEBELAGE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>180992464</t>
+          <t xml:space="preserve">LEBELAGE - Dr. Hyaluronic Derma Eye Cream [40ml] / Крем для </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
+          <t>8809445616522</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>126</v>
-      </c>
-      <c r="E39" t="n">
-        <v>20</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="E39" s="2" t="n"/>
       <c r="F39">
-        <f>E39*$J$3</f>
-        <v/>
-      </c>
-      <c r="G39">
-        <f>IF(F39=0,"",ROUND(D39/(F39/30),0))</f>
-        <v/>
-      </c>
-      <c r="H39">
-        <f>MAX(0,ROUND(F39*$J$2-D39,0))</f>
-        <v/>
-      </c>
-      <c r="I39">
-        <f>H39*$J$4/1000</f>
+        <f>D39*E39</f>
+        <v/>
+      </c>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="n"/>
+      <c r="J39">
+        <f>IF(G39="","",ROUNDUP(D39/G39,0))</f>
+        <v/>
+      </c>
+      <c r="K39">
+        <f>IF(J39="","",J39*H39)</f>
+        <v/>
+      </c>
+      <c r="L39">
+        <f>IF(J39="","",J39*I39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LEBELAGE</t>
+          <t>ISNTREE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>207818642</t>
+          <t>ISNTREE - Chestnut AHA 8% Clear Essence Sample [20ml] / Увла</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Hyaluronic Derma Eye Cream [40ml] / Крем</t>
+          <t>8809088970357</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>39</v>
-      </c>
-      <c r="E40" t="n">
-        <v>19</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="E40" s="2" t="n"/>
       <c r="F40">
-        <f>E40*$J$3</f>
-        <v/>
-      </c>
-      <c r="G40">
-        <f>IF(F40=0,"",ROUND(D40/(F40/30),0))</f>
-        <v/>
-      </c>
-      <c r="H40">
-        <f>MAX(0,ROUND(F40*$J$2-D40,0))</f>
-        <v/>
-      </c>
-      <c r="I40">
-        <f>H40*$J$4/1000</f>
+        <f>D40*E40</f>
+        <v/>
+      </c>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40">
+        <f>IF(G40="","",ROUNDUP(D40/G40,0))</f>
+        <v/>
+      </c>
+      <c r="K40">
+        <f>IF(J40="","",J40*H40)</f>
+        <v/>
+      </c>
+      <c r="L40">
+        <f>IF(J40="","",J40*I40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ISNTREE</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>207818000</t>
+          <t>ROUND LAB SOYBEAN CLEANSING OIL_200ml - Гидрофильное масло д</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ISNTREE - Chestnut AHA 8% Clear Essence Sample [20ml] /</t>
+          <t>8809783322130</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>60</v>
-      </c>
-      <c r="E41" t="n">
-        <v>15</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="E41" s="2" t="n"/>
       <c r="F41">
-        <f>E41*$J$3</f>
-        <v/>
-      </c>
-      <c r="G41">
-        <f>IF(F41=0,"",ROUND(D41/(F41/30),0))</f>
-        <v/>
-      </c>
-      <c r="H41">
-        <f>MAX(0,ROUND(F41*$J$2-D41,0))</f>
-        <v/>
-      </c>
-      <c r="I41">
-        <f>H41*$J$4/1000</f>
+        <f>D41*E41</f>
+        <v/>
+      </c>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41">
+        <f>IF(G41="","",ROUNDUP(D41/G41,0))</f>
+        <v/>
+      </c>
+      <c r="K41">
+        <f>IF(J41="","",J41*H41)</f>
+        <v/>
+      </c>
+      <c r="L41">
+        <f>IF(J41="","",J41*I41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>437850261</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Конси</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ROUND LAB SOYBEAN CLEANSING OIL_200ml - Гидрофильное ма</t>
+          <t>8809605872270</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>30</v>
-      </c>
-      <c r="E42" t="n">
-        <v>14</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="E42" s="2" t="n"/>
       <c r="F42">
-        <f>E42*$J$3</f>
-        <v/>
-      </c>
-      <c r="G42">
-        <f>IF(F42=0,"",ROUND(D42/(F42/30),0))</f>
-        <v/>
-      </c>
-      <c r="H42">
-        <f>MAX(0,ROUND(F42*$J$2-D42,0))</f>
-        <v/>
-      </c>
-      <c r="I42">
-        <f>H42*$J$4/1000</f>
+        <f>D42*E42</f>
+        <v/>
+      </c>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42">
+        <f>IF(G42="","",ROUNDUP(D42/G42,0))</f>
+        <v/>
+      </c>
+      <c r="K42">
+        <f>IF(J42="","",J42*H42)</f>
+        <v/>
+      </c>
+      <c r="L42">
+        <f>IF(J42="","",J42*I42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>611744611</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>5</v>
-      </c>
-      <c r="E43" t="n">
-        <v>8</v>
-      </c>
-      <c r="F43">
-        <f>E43*$J$3</f>
-        <v/>
-      </c>
-      <c r="G43">
-        <f>IF(F43=0,"",ROUND(D43/(F43/30),0))</f>
-        <v/>
-      </c>
-      <c r="H43">
-        <f>MAX(0,ROUND(F43*$J$2-D43,0))</f>
-        <v/>
-      </c>
-      <c r="I43">
-        <f>H43*$J$4/1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" s="1" t="inlineStr">
+      <c r="B43" s="1" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H44" s="1">
-        <f>SUM(H3:H43)</f>
-        <v/>
-      </c>
-      <c r="I44" s="1">
-        <f>SUM(I3:I43)</f>
+      <c r="D43" s="1">
+        <f>SUM(D2:D42)</f>
+        <v/>
+      </c>
+      <c r="F43" s="1">
+        <f>SUM(F2:F42)</f>
+        <v/>
+      </c>
+      <c r="K43" s="1">
+        <f>SUM(K2:K42)</f>
+        <v/>
+      </c>
+      <c r="L43" s="1">
+        <f>SUM(L2:L42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Вес контейнера, т</t>
+        </is>
+      </c>
+      <c r="D45">
+        <f>L43/1000</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Проверка веса, т</t>
-        </is>
-      </c>
-      <c r="D46">
-        <f>I44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Проверка штук</t>
-        </is>
-      </c>
-      <c r="D47">
-        <f>H44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>FarmStay исключён. Контейнер = позиции с покрытием &lt;150 дней, докуп до 6 мес спроса 2 магазинов.</t>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Лимит 26т/120к шт | транзит 2 мес | цель 6 мес | FarmStay искл. Жёлтые=ввод цены/короба (нет в заказе 22.06).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G3:G43">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
-      <formula>90</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/coverage/pokrytie_po_brendam_2026-06-30.xlsx
+++ b/outputs/coverage/pokrytie_po_brendam_2026-06-30.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Покрытие" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Новый контейнер" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,12 +32,8 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00C55A11"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -55,16 +50,6 @@
         <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C55A11"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -78,19 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -473,28 +451,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L175"/>
+  <dimension ref="A1:N175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Множитель (2 маг)</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="n">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Множитель 2 маг</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="n">
         <v>1.65</v>
       </c>
     </row>
@@ -521,7 +499,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Заказ 22.06</t>
+          <t>Заказ</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -536,12 +514,12 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Продажи/мес (Ракета)</t>
+          <t>Продажи/мес (Ракета 2026)</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Спрос 2 маг/мес</t>
+          <t>Спрос 2маг/мес</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -563,7 +541,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>COSRX - Advanced Snail 96 Mucin Power Essence [100ml] / Высо</t>
+          <t>COSRX - Advanced Snail 96 Mucin Power Essence [100ml] /</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -583,7 +561,7 @@
         <v>46</v>
       </c>
       <c r="I3">
-        <f>H3*$L$1</f>
+        <f>H3*$N$1</f>
         <v/>
       </c>
       <c r="J3">
@@ -604,7 +582,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>COSRX - Salicylic Acid Daily Gentle Cleanser [150ml] / Пенка</t>
+          <t xml:space="preserve">COSRX - Salicylic Acid Daily Gentle Cleanser [150ml] / </t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -624,7 +602,7 @@
         <v>44</v>
       </c>
       <c r="I4">
-        <f>H4*$L$1</f>
+        <f>H4*$N$1</f>
         <v/>
       </c>
       <c r="J4">
@@ -662,10 +640,10 @@
         <v/>
       </c>
       <c r="H5" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I5">
-        <f>H5*$L$1</f>
+        <f>H5*$N$1</f>
         <v/>
       </c>
       <c r="J5">
@@ -686,7 +664,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]/ Шам</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [200ml]</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -703,10 +681,10 @@
         <v/>
       </c>
       <c r="H6" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I6">
-        <f>H6*$L$1</f>
+        <f>H6*$N$1</f>
         <v/>
       </c>
       <c r="J6">
@@ -727,7 +705,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml] мягк</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml]</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -747,7 +725,7 @@
         <v>39</v>
       </c>
       <c r="I7">
-        <f>H7*$L$1</f>
+        <f>H7*$N$1</f>
         <v/>
       </c>
       <c r="J7">
@@ -768,7 +746,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml] мягк</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml]</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -785,10 +763,10 @@
         <v/>
       </c>
       <c r="H8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8">
-        <f>H8*$L$1</f>
+        <f>H8*$N$1</f>
         <v/>
       </c>
       <c r="J8">
@@ -809,7 +787,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DEOPROCE - SNAIL RECOVERY CREAM [100g] / Крем восстанавливаю</t>
+          <t>DEOPROCE - SNAIL RECOVERY CREAM [100g] / Крем восстанав</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -829,7 +807,7 @@
         <v>22</v>
       </c>
       <c r="I9">
-        <f>H9*$L$1</f>
+        <f>H9*$N$1</f>
         <v/>
       </c>
       <c r="J9">
@@ -850,7 +828,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DR. JART - Ctrl+A Teatreatment Toner [120ml] / Тонер тоник д</t>
+          <t>DR. JART - Ctrl+A Teatreatment Toner [120ml] / Тонер то</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -870,7 +848,7 @@
         <v>15</v>
       </c>
       <c r="I10">
-        <f>H10*$L$1</f>
+        <f>H10*$N$1</f>
         <v/>
       </c>
       <c r="J10">
@@ -891,7 +869,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EKEL - Ampule Сream Сollagen [70ml] / Крем для лица ампульны</t>
+          <t>EKEL - Ampule Сream Сollagen [70ml] / Крем для лица амп</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -908,10 +886,10 @@
         <v/>
       </c>
       <c r="H11" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I11">
-        <f>H11*$L$1</f>
+        <f>H11*$N$1</f>
         <v/>
       </c>
       <c r="J11">
@@ -932,7 +910,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - Aqua Hyaluronic Acid Water Drop Cream / Увлажня</t>
+          <t>ELIZAVECCA - Aqua Hyaluronic Acid Water Drop Cream / Ув</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -949,10 +927,10 @@
         <v/>
       </c>
       <c r="H12" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="I12">
-        <f>H12*$L$1</f>
+        <f>H12*$N$1</f>
         <v/>
       </c>
       <c r="J12">
@@ -973,7 +951,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - Natural 90% Olive Cleansing Oil / Очищающее гид</t>
+          <t>ELIZAVECCA - Natural 90% Olive Cleansing Oil / Очищающе</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -990,10 +968,10 @@
         <v/>
       </c>
       <c r="H13" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I13">
-        <f>H13*$L$1</f>
+        <f>H13*$N$1</f>
         <v/>
       </c>
       <c r="J13">
@@ -1014,7 +992,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - Hell pore clean up aha fruit toner [ 200ml] / П</t>
+          <t>ELIZAVECCA - Hell pore clean up aha fruit toner [ 200ml</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1031,10 +1009,10 @@
         <v/>
       </c>
       <c r="H14" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I14">
-        <f>H14*$L$1</f>
+        <f>H14*$N$1</f>
         <v/>
       </c>
       <c r="J14">
@@ -1055,7 +1033,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - 24K Gold Snail Cleansing Foam [180ml] / Золотая</t>
+          <t>ELIZAVECCA - 24K Gold Snail Cleansing Foam [180ml] / Зо</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1072,10 +1050,10 @@
         <v/>
       </c>
       <c r="H15" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I15">
-        <f>H15*$L$1</f>
+        <f>H15*$N$1</f>
         <v/>
       </c>
       <c r="J15">
@@ -1096,7 +1074,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein Treat</t>
+          <t xml:space="preserve">ELIZAVECCA - CER-100 Collagen Ceramide Coating Protein </t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1113,10 +1091,10 @@
         <v/>
       </c>
       <c r="H16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I16">
-        <f>H16*$L$1</f>
+        <f>H16*$N$1</f>
         <v/>
       </c>
       <c r="J16">
@@ -1132,16 +1110,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>206058262</t>
+          <t>190160008</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - Hell-Pore Galactomyces Pure Ample / Сыворотка д</t>
+          <t xml:space="preserve">ELIZAVECCA - Milky Piggy EGF elastic retinol [100ml] / </t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>178</v>
+        <v>451</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1157,7 +1135,7 @@
         <v>4</v>
       </c>
       <c r="I17">
-        <f>H17*$L$1</f>
+        <f>H17*$N$1</f>
         <v/>
       </c>
       <c r="J17">
@@ -1173,16 +1151,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>190160008</t>
+          <t>206058262</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - Milky Piggy EGF elastic retinol [100ml] / Антив</t>
+          <t>ELIZAVECCA - Hell-Pore Galactomyces Pure Ample / Сыворо</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>451</v>
+        <v>178</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1198,7 +1176,7 @@
         <v>3</v>
       </c>
       <c r="I18">
-        <f>H18*$L$1</f>
+        <f>H18*$N$1</f>
         <v/>
       </c>
       <c r="J18">
@@ -1219,7 +1197,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увлажняю</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] / Увл</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1236,10 +1214,10 @@
         <v/>
       </c>
       <c r="H19" t="n">
-        <v>1315</v>
+        <v>1392</v>
       </c>
       <c r="I19">
-        <f>H19*$L$1</f>
+        <f>H19*$N$1</f>
         <v/>
       </c>
       <c r="J19">
@@ -1260,7 +1238,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen 3in1 Sun Cream SPF50 PA+++ [50ml] / отбели</t>
+          <t>ENOUGH - Collagen 3in1 Sun Cream SPF50 PA+++ [50ml] / о</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1277,10 +1255,10 @@
         <v/>
       </c>
       <c r="H20" t="n">
-        <v>539</v>
+        <v>594</v>
       </c>
       <c r="I20">
-        <f>H20*$L$1</f>
+        <f>H20*$N$1</f>
         <v/>
       </c>
       <c r="J20">
@@ -1301,7 +1279,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13] / Тональны</t>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13] / Тон</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1318,10 +1296,10 @@
         <v/>
       </c>
       <c r="H21" t="n">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="I21">
-        <f>H21*$L$1</f>
+        <f>H21*$N$1</f>
         <v/>
       </c>
       <c r="J21">
@@ -1342,7 +1320,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENOUGH - Collagen Moisture Foundation [Tone 13] / Тональный </t>
+          <t>ENOUGH - Collagen Moisture Foundation [Tone 13] / Тонал</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1359,10 +1337,10 @@
         <v/>
       </c>
       <c r="H22" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="I22">
-        <f>H22*$L$1</f>
+        <f>H22*$N$1</f>
         <v/>
       </c>
       <c r="J22">
@@ -1383,7 +1361,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21] / Тональны</t>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21] / Тон</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1403,7 +1381,7 @@
         <v>175</v>
       </c>
       <c r="I23">
-        <f>H23*$L$1</f>
+        <f>H23*$N$1</f>
         <v/>
       </c>
       <c r="J23">
@@ -1424,7 +1402,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ENOUGH - Premium 8 Peptide Full Cover Perfect Foundation [To</t>
+          <t>ENOUGH - Premium 8 Peptide Full Cover Perfect Foundatio</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1441,10 +1419,10 @@
         <v/>
       </c>
       <c r="H24" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="I24">
-        <f>H24*$L$1</f>
+        <f>H24*$N$1</f>
         <v/>
       </c>
       <c r="J24">
@@ -1460,32 +1438,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>170198180</t>
+          <t>170198835</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundation [</t>
+          <t>ENOUGH - Premium Ultra X10 Cover Up Collagen Foundation</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>427</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="G25">
         <f>D25+E25+F25</f>
         <v/>
       </c>
       <c r="H25" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I25">
-        <f>H25*$L$1</f>
+        <f>H25*$N$1</f>
         <v/>
       </c>
       <c r="J25">
@@ -1501,32 +1479,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>170198835</t>
+          <t>238416010</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ENOUGH - Premium Ultra X10 Cover Up Collagen Foundation [Ton</t>
+          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] /</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1221</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G26">
         <f>D26+E26+F26</f>
         <v/>
       </c>
       <c r="H26" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I26">
-        <f>H26*$L$1</f>
+        <f>H26*$N$1</f>
         <v/>
       </c>
       <c r="J26">
@@ -1542,22 +1520,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>238416010</t>
+          <t>170198180</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Whitening Moisture Cream 3in1 [50g] / Анти</t>
+          <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundat</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1221</v>
+        <v>427</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G27">
         <f>D27+E27+F27</f>
@@ -1567,7 +1545,7 @@
         <v>125</v>
       </c>
       <c r="I27">
-        <f>H27*$L$1</f>
+        <f>H27*$N$1</f>
         <v/>
       </c>
       <c r="J27">
@@ -1588,7 +1566,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundation [</t>
+          <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundat</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1605,10 +1583,10 @@
         <v/>
       </c>
       <c r="H28" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="I28">
-        <f>H28*$L$1</f>
+        <f>H28*$N$1</f>
         <v/>
       </c>
       <c r="J28">
@@ -1624,16 +1602,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>170198738</t>
+          <t>238413828</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ENOUGH - Premium 8 Peptide Full Cover Perfect Foundation [To</t>
+          <t xml:space="preserve">ENOUGH - Collagen Moisture BB Cream SPF47 PA+++ [50ml] </t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1580</v>
+        <v>1378</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1646,10 +1624,10 @@
         <v/>
       </c>
       <c r="H29" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I29">
-        <f>H29*$L$1</f>
+        <f>H29*$N$1</f>
         <v/>
       </c>
       <c r="J29">
@@ -1665,19 +1643,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>238413828</t>
+          <t>170198876</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture BB Cream SPF47 PA+++ [50ml] / Увл</t>
+          <t>ENOUGH - Premium Ultra X10 Cover Up Collagen Foundation</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1378</v>
+        <v>78</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1687,10 +1665,10 @@
         <v/>
       </c>
       <c r="H30" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I30">
-        <f>H30*$L$1</f>
+        <f>H30*$N$1</f>
         <v/>
       </c>
       <c r="J30">
@@ -1706,19 +1684,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>170198876</t>
+          <t>150925322</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ENOUGH - Premium Ultra X10 Cover Up Collagen Foundation [Ton</t>
+          <t>ENOUGH - Collagen Moisture Foundation [Tone 21] / Тонал</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>78</v>
+        <v>3099</v>
       </c>
       <c r="E31" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1728,10 +1706,10 @@
         <v/>
       </c>
       <c r="H31" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I31">
-        <f>H31*$L$1</f>
+        <f>H31*$N$1</f>
         <v/>
       </c>
       <c r="J31">
@@ -1747,16 +1725,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>150925322</t>
+          <t>170198738</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENOUGH - Collagen Moisture Foundation [Tone 21] / Тональный </t>
+          <t>ENOUGH - Premium 8 Peptide Full Cover Perfect Foundatio</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3099</v>
+        <v>1580</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -1772,7 +1750,7 @@
         <v>88</v>
       </c>
       <c r="I32">
-        <f>H32*$L$1</f>
+        <f>H32*$N$1</f>
         <v/>
       </c>
       <c r="J32">
@@ -1793,7 +1771,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen 3in1 Whitening Moisture Foundation [Tone 1</t>
+          <t>ENOUGH - Collagen 3in1 Whitening Moisture Foundation [T</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1810,10 +1788,10 @@
         <v/>
       </c>
       <c r="H33" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I33">
-        <f>H33*$L$1</f>
+        <f>H33*$N$1</f>
         <v/>
       </c>
       <c r="J33">
@@ -1829,16 +1807,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>151132052</t>
+          <t>611747838</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen 3in1 Whitening Moisture Foundation [Tone 2</t>
+          <t>ENOUGH - Collagen Moisture Foundation [Tone 23] / Тонал</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>769</v>
+        <v>90</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -1854,7 +1832,7 @@
         <v>35</v>
       </c>
       <c r="I34">
-        <f>H34*$L$1</f>
+        <f>H34*$N$1</f>
         <v/>
       </c>
       <c r="J34">
@@ -1870,16 +1848,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>611747838</t>
+          <t>151132052</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENOUGH - Collagen Moisture Foundation [Tone 23] / Тональный </t>
+          <t>ENOUGH - Collagen 3in1 Whitening Moisture Foundation [T</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>90</v>
+        <v>769</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -1892,10 +1870,10 @@
         <v/>
       </c>
       <c r="H35" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I35">
-        <f>H35*$L$1</f>
+        <f>H35*$N$1</f>
         <v/>
       </c>
       <c r="J35">
@@ -1916,7 +1894,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Конси</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1933,10 +1911,10 @@
         <v/>
       </c>
       <c r="H36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I36">
-        <f>H36*$L$1</f>
+        <f>H36*$N$1</f>
         <v/>
       </c>
       <c r="J36">
@@ -1957,7 +1935,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/ Конс</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #03 [9g]/</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1977,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <f>H37*$L$1</f>
+        <f>H37*$N$1</f>
         <v/>
       </c>
       <c r="J37">
@@ -1998,7 +1976,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очищающий </t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml] / Очища</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -2015,10 +1993,10 @@
         <v/>
       </c>
       <c r="H38" t="n">
-        <v>766</v>
+        <v>785</v>
       </c>
       <c r="I38">
-        <f>H38*$L$1</f>
+        <f>H38*$N$1</f>
         <v/>
       </c>
       <c r="J38">
@@ -2039,7 +2017,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [24*7ml] / Очищающий</t>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [24*7ml] / Очищ</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2056,10 +2034,10 @@
         <v/>
       </c>
       <c r="H39" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I39">
-        <f>H39*$L$1</f>
+        <f>H39*$N$1</f>
         <v/>
       </c>
       <c r="J39">
@@ -2075,16 +2053,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>154159632</t>
+          <t>307073881</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETUDE - Baking Powder BB Deep Cleansing Foam [30ml] / Пенка </t>
+          <t xml:space="preserve">ETUDE - Baking Powder BB Deep Cleansing Foam [160ml] / </t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>175</v>
+        <v>392</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -2097,10 +2075,10 @@
         <v/>
       </c>
       <c r="H40" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I40">
-        <f>H40*$L$1</f>
+        <f>H40*$N$1</f>
         <v/>
       </c>
       <c r="J40">
@@ -2116,16 +2094,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>307073881</t>
+          <t>154159632</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ETUDE - Baking Powder BB Deep Cleansing Foam [160ml] / Пенка</t>
+          <t>ETUDE - Baking Powder BB Deep Cleansing Foam [30ml] / П</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>392</v>
+        <v>175</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -2138,10 +2116,10 @@
         <v/>
       </c>
       <c r="H41" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I41">
-        <f>H41*$L$1</f>
+        <f>H41*$N$1</f>
         <v/>
       </c>
       <c r="J41">
@@ -2162,7 +2140,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoule [25</t>
+          <t>FARMSTAY - Collagen &amp; Hyaluronic Acid All-In One Ampoul</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2179,10 +2157,10 @@
         <v/>
       </c>
       <c r="H42" t="n">
-        <v>1668</v>
+        <v>1692</v>
       </c>
       <c r="I42">
-        <f>H42*$L$1</f>
+        <f>H42*$N$1</f>
         <v/>
       </c>
       <c r="J42">
@@ -2203,7 +2181,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Шампунь</t>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] / Ша</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2220,10 +2198,10 @@
         <v/>
       </c>
       <c r="H43" t="n">
-        <v>1050</v>
+        <v>1069</v>
       </c>
       <c r="I43">
-        <f>H43*$L$1</f>
+        <f>H43*$N$1</f>
         <v/>
       </c>
       <c r="J43">
@@ -2244,7 +2222,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Крем с </t>
+          <t>FARMSTAY - Escargot Noblesse Intensive Cream [50g] / Кр</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2261,10 +2239,10 @@
         <v/>
       </c>
       <c r="H44" t="n">
-        <v>530</v>
+        <v>554</v>
       </c>
       <c r="I44">
-        <f>H44*$L$1</f>
+        <f>H44*$N$1</f>
         <v/>
       </c>
       <c r="J44">
@@ -2285,7 +2263,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживающий к</t>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml] / Омолаживаю</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2302,10 +2280,10 @@
         <v/>
       </c>
       <c r="H45" t="n">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="I45">
-        <f>H45*$L$1</f>
+        <f>H45*$N$1</f>
         <v/>
       </c>
       <c r="J45">
@@ -2326,7 +2304,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Conditione</t>
+          <t>FARMSTAY - Argan Oil Complete Volume Up Shampoo &amp; Condi</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2343,10 +2321,10 @@
         <v/>
       </c>
       <c r="H46" t="n">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="I46">
-        <f>H46*$L$1</f>
+        <f>H46*$N$1</f>
         <v/>
       </c>
       <c r="J46">
@@ -2367,7 +2345,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [530ml]</t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [5</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2384,10 +2362,10 @@
         <v/>
       </c>
       <c r="H47" t="n">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="I47">
-        <f>H47*$L$1</f>
+        <f>H47*$N$1</f>
         <v/>
       </c>
       <c r="J47">
@@ -2408,7 +2386,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка с ул</t>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE/ сыворотка</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2425,10 +2403,10 @@
         <v/>
       </c>
       <c r="H48" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I48">
-        <f>H48*$L$1</f>
+        <f>H48*$N$1</f>
         <v/>
       </c>
       <c r="J48">
@@ -2449,7 +2427,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увлажняю</t>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g] / Увл</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2466,10 +2444,10 @@
         <v/>
       </c>
       <c r="H49" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="I49">
-        <f>H49*$L$1</f>
+        <f>H49*$N$1</f>
         <v/>
       </c>
       <c r="J49">
@@ -2490,7 +2468,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка для ум</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]/Пенка д</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2507,10 +2485,10 @@
         <v/>
       </c>
       <c r="H50" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I50">
-        <f>H50*$L$1</f>
+        <f>H50*$N$1</f>
         <v/>
       </c>
       <c r="J50">
@@ -2531,7 +2509,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Rolling Eye Serum [25ml</t>
+          <t xml:space="preserve">FARMSTAY - Collagen Water Full Moist Rolling Eye Serum </t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2548,10 +2526,10 @@
         <v/>
       </c>
       <c r="H51" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I51">
-        <f>H51*$L$1</f>
+        <f>H51*$N$1</f>
         <v/>
       </c>
       <c r="J51">
@@ -2572,7 +2550,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] / Баз</t>
+          <t xml:space="preserve">HEIMISH - Artless Glow Base SPF50+ PA+++(Renew) [40ml] </t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2589,10 +2567,10 @@
         <v/>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="I52">
-        <f>H52*$L$1</f>
+        <f>H52*$N$1</f>
         <v/>
       </c>
       <c r="J52">
@@ -2613,7 +2591,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HEIMISH - All Clean Balm Mandarin [120ml] / Очищающий гидроф</t>
+          <t>HEIMISH - All Clean Balm Mandarin [120ml] / Очищающий г</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2630,10 +2608,10 @@
         <v/>
       </c>
       <c r="H53" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I53">
-        <f>H53*$L$1</f>
+        <f>H53*$N$1</f>
         <v/>
       </c>
       <c r="J53">
@@ -2654,7 +2632,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>I'm Sorry For My Skin - Age Capture Vitalizer Cream / Увлажн</t>
+          <t>I'm Sorry For My Skin - Age Capture Vitalizer Cream / У</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2674,7 +2652,7 @@
         <v>52</v>
       </c>
       <c r="I54">
-        <f>H54*$L$1</f>
+        <f>H54*$N$1</f>
         <v/>
       </c>
       <c r="J54">
@@ -2695,7 +2673,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>I'm Sorry For My Skin - Age Capture Hydrating Cream / Увлажн</t>
+          <t>I'm Sorry For My Skin - Age Capture Hydrating Cream / У</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2712,10 +2690,10 @@
         <v/>
       </c>
       <c r="H55" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I55">
-        <f>H55*$L$1</f>
+        <f>H55*$N$1</f>
         <v/>
       </c>
       <c r="J55">
@@ -2731,19 +2709,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>206125905</t>
+          <t>206122859</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>I'm Sorry For My Skin - Age Capture Skin Relief Cream / Увла</t>
+          <t>I'm Sorry For My Skin - Age Capture Firming Enriched Cr</t>
         </is>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>320</v>
+        <v>560</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -2756,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <f>H56*$L$1</f>
+        <f>H56*$N$1</f>
         <v/>
       </c>
       <c r="J56">
@@ -2772,19 +2750,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>206122859</t>
+          <t>206125905</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>I'm Sorry For My Skin - Age Capture Firming Enriched Cream /</t>
+          <t>I'm Sorry For My Skin - Age Capture Skin Relief Cream /</t>
         </is>
       </c>
       <c r="D57" t="n">
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>560</v>
+        <v>320</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -2797,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <f>H57*$L$1</f>
+        <f>H57*$N$1</f>
         <v/>
       </c>
       <c r="J57">
@@ -2818,7 +2796,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ISNTREE - Chestnut AHA 8% Clear Essence Sample [20ml] / Увла</t>
+          <t>ISNTREE - Chestnut AHA 8% Clear Essence Sample [20ml] /</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2835,10 +2813,10 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I58">
-        <f>H58*$L$1</f>
+        <f>H58*$N$1</f>
         <v/>
       </c>
       <c r="J58">
@@ -2859,7 +2837,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увлажняю</t>
+          <t>JIGOTT - Snail Lifting Cream [70ml] / Крем для лица увл</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2876,10 +2854,10 @@
         <v/>
       </c>
       <c r="H59" t="n">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="I59">
-        <f>H59*$L$1</f>
+        <f>H59*$N$1</f>
         <v/>
       </c>
       <c r="J59">
@@ -2900,7 +2878,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажн</t>
+          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица у</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2917,10 +2895,10 @@
         <v/>
       </c>
       <c r="H60" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="I60">
-        <f>H60*$L$1</f>
+        <f>H60*$N$1</f>
         <v/>
       </c>
       <c r="J60">
@@ -2941,7 +2919,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица с це</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml] / Тонер для лица</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2958,10 +2936,10 @@
         <v/>
       </c>
       <c r="H61" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I61">
-        <f>H61*$L$1</f>
+        <f>H61*$N$1</f>
         <v/>
       </c>
       <c r="J61">
@@ -2982,7 +2960,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастной кр</t>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml] / Антивозрастн</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2999,10 +2977,10 @@
         <v/>
       </c>
       <c r="H62" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I62">
-        <f>H62*$L$1</f>
+        <f>H62*$N$1</f>
         <v/>
       </c>
       <c r="J62">
@@ -3023,7 +3001,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с колл</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml] / тонер с</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -3040,10 +3018,10 @@
         <v/>
       </c>
       <c r="H63" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I63">
-        <f>H63*$L$1</f>
+        <f>H63*$N$1</f>
         <v/>
       </c>
       <c r="J63">
@@ -3064,7 +3042,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер для л</t>
+          <t xml:space="preserve">JIGOTT - Moisture Real Aloe Vera Toner [300ml] / Тонер </t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -3084,7 +3062,7 @@
         <v>47</v>
       </c>
       <c r="I64">
-        <f>H64*$L$1</f>
+        <f>H64*$N$1</f>
         <v/>
       </c>
       <c r="J64">
@@ -3105,7 +3083,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>JIGOTT - Aura Secret Hyaluronec Acid Toner [300ml] / Тонер с</t>
+          <t>JIGOTT - Aura Secret Hyaluronec Acid Toner [300ml] / То</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -3125,7 +3103,7 @@
         <v>42</v>
       </c>
       <c r="I65">
-        <f>H65*$L$1</f>
+        <f>H65*$N$1</f>
         <v/>
       </c>
       <c r="J65">
@@ -3146,7 +3124,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JIGOTT - Collagen Healing Cream [100ml] / Крем для лица с ко</t>
+          <t>JIGOTT - Collagen Healing Cream [100ml] / Крем для лица</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -3163,10 +3141,10 @@
         <v/>
       </c>
       <c r="H66" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I66">
-        <f>H66*$L$1</f>
+        <f>H66*$N$1</f>
         <v/>
       </c>
       <c r="J66">
@@ -3187,7 +3165,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">JMSOLUTION - Marine Luminous Pearl Deep Moisture Mask Pearl </t>
+          <t>JMSOLUTION - Marine Luminous Pearl Deep Moisture Mask P</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -3204,10 +3182,10 @@
         <v/>
       </c>
       <c r="H67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I67">
-        <f>H67*$L$1</f>
+        <f>H67*$N$1</f>
         <v/>
       </c>
       <c r="J67">
@@ -3228,7 +3206,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем для гла</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml] / Крем дл</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -3248,7 +3226,7 @@
         <v>21</v>
       </c>
       <c r="I68">
-        <f>H68*$L$1</f>
+        <f>H68*$N$1</f>
         <v/>
       </c>
       <c r="J68">
@@ -3269,7 +3247,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEBELAGE - Dr. Hyaluronic Derma Eye Cream [40ml] / Крем для </t>
+          <t>LEBELAGE - Dr. Hyaluronic Derma Eye Cream [40ml] / Крем</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -3286,10 +3264,10 @@
         <v/>
       </c>
       <c r="H69" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I69">
-        <f>H69*$L$1</f>
+        <f>H69*$N$1</f>
         <v/>
       </c>
       <c r="J69">
@@ -3310,7 +3288,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыво</t>
+          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -3327,10 +3305,10 @@
         <v/>
       </c>
       <c r="H70" t="n">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="I70">
-        <f>H70*$L$1</f>
+        <f>H70*$N$1</f>
         <v/>
       </c>
       <c r="J70">
@@ -3351,7 +3329,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозрастная</t>
+          <t>MANYO - Bifida Biome Complex Ampoule [50ml] / Антивозра</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -3368,10 +3346,10 @@
         <v/>
       </c>
       <c r="H71" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I71">
-        <f>H71*$L$1</f>
+        <f>H71*$N$1</f>
         <v/>
       </c>
       <c r="J71">
@@ -3392,7 +3370,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Ampoule Toner [400ml] / Ампульный укреп</t>
+          <t xml:space="preserve">MANYO - Bifida Biome Ampoule Toner [400ml] / Ампульный </t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -3409,10 +3387,10 @@
         <v/>
       </c>
       <c r="H72" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I72">
-        <f>H72*$L$1</f>
+        <f>H72*$N$1</f>
         <v/>
       </c>
       <c r="J72">
@@ -3433,7 +3411,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для </t>
+          <t>MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -3450,10 +3428,10 @@
         <v/>
       </c>
       <c r="H73" t="n">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="I73">
-        <f>H73*$L$1</f>
+        <f>H73*$N$1</f>
         <v/>
       </c>
       <c r="J73">
@@ -3474,7 +3452,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гель для</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml] / Гел</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3491,10 +3469,10 @@
         <v/>
       </c>
       <c r="H74" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="I74">
-        <f>H74*$L$1</f>
+        <f>H74*$N$1</f>
         <v/>
       </c>
       <c r="J74">
@@ -3515,7 +3493,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворотка с </t>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml] / Сыворот</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3532,10 +3510,10 @@
         <v/>
       </c>
       <c r="H75" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I75">
-        <f>H75*$L$1</f>
+        <f>H75*$N$1</f>
         <v/>
       </c>
       <c r="J75">
@@ -3556,7 +3534,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющий ло</t>
+          <t>MANYO - Bifida Biome Ampoule Lotion [300ml] / Укрепляющ</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3573,10 +3551,10 @@
         <v/>
       </c>
       <c r="H76" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="I76">
-        <f>H76*$L$1</f>
+        <f>H76*$N$1</f>
         <v/>
       </c>
       <c r="J76">
@@ -3597,7 +3575,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MASIL - 8 Seconds Salon Hair Mask 350ml Set [350ml+8ml*2]</t>
+          <t>MASIL - 8 Seconds Salon Hair Mask 350ml Set [350ml+8ml*</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3614,10 +3592,10 @@
         <v/>
       </c>
       <c r="H77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I77">
-        <f>H77*$L$1</f>
+        <f>H77*$N$1</f>
         <v/>
       </c>
       <c r="J77">
@@ -3638,7 +3616,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Ги</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea]</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3655,10 +3633,10 @@
         <v/>
       </c>
       <c r="H78" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="I78">
-        <f>H78*$L$1</f>
+        <f>H78*$N$1</f>
         <v/>
       </c>
       <c r="J78">
@@ -3679,7 +3657,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлажда</t>
+          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Ох</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3696,10 +3674,10 @@
         <v/>
       </c>
       <c r="H79" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="I79">
-        <f>H79*$L$1</f>
+        <f>H79*$N$1</f>
         <v/>
       </c>
       <c r="J79">
@@ -3720,7 +3698,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Охлажда</t>
+          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea] / Ох</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3737,10 +3715,10 @@
         <v/>
       </c>
       <c r="H80" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I80">
-        <f>H80*$L$1</f>
+        <f>H80*$N$1</f>
         <v/>
       </c>
       <c r="J80">
@@ -3761,7 +3739,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гидрогел</t>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Eye Patch [60ea] / Гид</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3778,10 +3756,10 @@
         <v/>
       </c>
       <c r="H81" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I81">
-        <f>H81*$L$1</f>
+        <f>H81*$N$1</f>
         <v/>
       </c>
       <c r="J81">
@@ -3802,7 +3780,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">PETITFEE - Chamomile Lightening Hydrogel Mask Pack [5pcs] / </t>
+          <t>PETITFEE - Chamomile Lightening Hydrogel Mask Pack [5pc</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3822,7 +3800,7 @@
         <v>88</v>
       </c>
       <c r="I82">
-        <f>H82*$L$1</f>
+        <f>H82*$N$1</f>
         <v/>
       </c>
       <c r="J82">
@@ -3843,7 +3821,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гидрогел</t>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs] / Гид</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3860,10 +3838,10 @@
         <v/>
       </c>
       <c r="H83" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I83">
-        <f>H83*$L$1</f>
+        <f>H83*$N$1</f>
         <v/>
       </c>
       <c r="J83">
@@ -3884,7 +3862,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелевая мас</t>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs] / Гидрогелева</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3904,7 +3882,7 @@
         <v>65</v>
       </c>
       <c r="I84">
-        <f>H84*$L$1</f>
+        <f>H84*$N$1</f>
         <v/>
       </c>
       <c r="J84">
@@ -3925,7 +3903,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea] / </t>
+          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60e</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3942,10 +3920,10 @@
         <v/>
       </c>
       <c r="H85" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I85">
-        <f>H85*$L$1</f>
+        <f>H85*$N$1</f>
         <v/>
       </c>
       <c r="J85">
@@ -3966,7 +3944,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / Ткане</t>
+          <t xml:space="preserve">PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea] / </t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3986,7 +3964,7 @@
         <v>47</v>
       </c>
       <c r="I86">
-        <f>H86*$L$1</f>
+        <f>H86*$N$1</f>
         <v/>
       </c>
       <c r="J86">
@@ -4007,7 +3985,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea] / См</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea]</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -4024,10 +4002,10 @@
         <v/>
       </c>
       <c r="H87" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I87">
-        <f>H87*$L$1</f>
+        <f>H87*$N$1</f>
         <v/>
       </c>
       <c r="J87">
@@ -4043,16 +4021,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>179611231</t>
+          <t>180711104</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] / Гидр</t>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевы</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1275</v>
+        <v>801</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -4065,10 +4043,10 @@
         <v/>
       </c>
       <c r="H88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I88">
-        <f>H88*$L$1</f>
+        <f>H88*$N$1</f>
         <v/>
       </c>
       <c r="J88">
@@ -4084,16 +4062,16 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>180711104</t>
+          <t>179611231</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [60ea] / гидрогелевые пат</t>
+          <t>PETITFEE - Collagen &amp; CoQ10 Hydrogel Eye Patch [60ea] /</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>801</v>
+        <v>1275</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -4106,10 +4084,10 @@
         <v/>
       </c>
       <c r="H89" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I89">
-        <f>H89*$L$1</f>
+        <f>H89*$N$1</f>
         <v/>
       </c>
       <c r="J89">
@@ -4130,7 +4108,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] / Тони</t>
+          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea] /</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -4150,7 +4128,7 @@
         <v>20</v>
       </c>
       <c r="I90">
-        <f>H90*$L$1</f>
+        <f>H90*$N$1</f>
         <v/>
       </c>
       <c r="J90">
@@ -4191,7 +4169,7 @@
         <v>20</v>
       </c>
       <c r="I91">
-        <f>H91*$L$1</f>
+        <f>H91*$N$1</f>
         <v/>
       </c>
       <c r="J91">
@@ -4212,7 +4190,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тканевые</t>
+          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea] / Тка</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -4232,7 +4210,7 @@
         <v>19</v>
       </c>
       <c r="I92">
-        <f>H92*$L$1</f>
+        <f>H92*$N$1</f>
         <v/>
       </c>
       <c r="J92">
@@ -4253,7 +4231,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; EGF Hydrogel Eye &amp; Spot Patch [60ea]/ гидр</t>
+          <t>PETITFEE - Gold &amp; EGF Hydrogel Eye &amp; Spot Patch [60ea]/</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -4273,7 +4251,7 @@
         <v>11</v>
       </c>
       <c r="I93">
-        <f>H93*$L$1</f>
+        <f>H93*$N$1</f>
         <v/>
       </c>
       <c r="J93">
@@ -4289,16 +4267,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>226114831</t>
+          <t>226115478</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs] / См</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs]</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>717</v>
+        <v>672</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -4314,7 +4292,7 @@
         <v>10</v>
       </c>
       <c r="I94">
-        <f>H94*$L$1</f>
+        <f>H94*$N$1</f>
         <v/>
       </c>
       <c r="J94">
@@ -4335,7 +4313,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] / Тони</t>
+          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs] /</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -4352,10 +4330,10 @@
         <v/>
       </c>
       <c r="H95" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I95">
-        <f>H95*$L$1</f>
+        <f>H95*$N$1</f>
         <v/>
       </c>
       <c r="J95">
@@ -4371,16 +4349,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>226115478</t>
+          <t>226114831</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs] / Ги</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs]</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>672</v>
+        <v>717</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -4393,10 +4371,10 @@
         <v/>
       </c>
       <c r="H96" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I96">
-        <f>H96*$L$1</f>
+        <f>H96*$N$1</f>
         <v/>
       </c>
       <c r="J96">
@@ -4417,7 +4395,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка для </t>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml - Увлажняющая пенка</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -4434,10 +4412,10 @@
         <v/>
       </c>
       <c r="H97" t="n">
-        <v>2258</v>
+        <v>2158</v>
       </c>
       <c r="I97">
-        <f>H97*$L$1</f>
+        <f>H97*$N$1</f>
         <v/>
       </c>
       <c r="J97">
@@ -4458,7 +4436,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пенка д</t>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml - Очищающая пе</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -4475,10 +4453,10 @@
         <v/>
       </c>
       <c r="H98" t="n">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="I98">
-        <f>H98*$L$1</f>
+        <f>H98*$N$1</f>
         <v/>
       </c>
       <c r="J98">
@@ -4499,7 +4477,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ROUND LAB SOYBEAN PANTHENOL CREAM_80ml - Крем для лица с чёр</t>
+          <t xml:space="preserve">ROUND LAB SOYBEAN PANTHENOL CREAM_80ml - Крем для лица </t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -4516,10 +4494,10 @@
         <v/>
       </c>
       <c r="H99" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="I99">
-        <f>H99*$L$1</f>
+        <f>H99*$N$1</f>
         <v/>
       </c>
       <c r="J99">
@@ -4540,7 +4518,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняющий к</t>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml -Увлажняю</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -4557,10 +4535,10 @@
         <v/>
       </c>
       <c r="H100" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I100">
-        <f>H100*$L$1</f>
+        <f>H100*$N$1</f>
         <v/>
       </c>
       <c r="J100">
@@ -4581,7 +4559,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROUND LAB VITA NIACINAMIDE DARK SPOT SERUM 30ml - Сыворотка </t>
+          <t>ROUND LAB VITA NIACINAMIDE DARK SPOT SERUM 30ml - Сывор</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -4601,7 +4579,7 @@
         <v>40</v>
       </c>
       <c r="I101">
-        <f>H101*$L$1</f>
+        <f>H101*$N$1</f>
         <v/>
       </c>
       <c r="J101">
@@ -4622,7 +4600,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жир</t>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка дл</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -4639,10 +4617,10 @@
         <v/>
       </c>
       <c r="H102" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I102">
-        <f>H102*$L$1</f>
+        <f>H102*$N$1</f>
         <v/>
       </c>
       <c r="J102">
@@ -4663,7 +4641,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ROUND LAB SOYBEAN CLEANSING OIL_200ml - Гидрофильное масло д</t>
+          <t>ROUND LAB SOYBEAN CLEANSING OIL_200ml - Гидрофильное ма</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4680,10 +4658,10 @@
         <v/>
       </c>
       <c r="H103" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I103">
-        <f>H103*$L$1</f>
+        <f>H103*$N$1</f>
         <v/>
       </c>
       <c r="J103">
@@ -4704,7 +4682,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник с мо</t>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml / Отшелушивающий тоник</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4721,10 +4699,10 @@
         <v/>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I104">
-        <f>H104*$L$1</f>
+        <f>H104*$N$1</f>
         <v/>
       </c>
       <c r="J104">
@@ -4745,7 +4723,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворотка дл</t>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml] / Сыворот</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4762,10 +4740,10 @@
         <v/>
       </c>
       <c r="H105" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I105">
-        <f>H105*$L$1</f>
+        <f>H105*$N$1</f>
         <v/>
       </c>
       <c r="J105">
@@ -4786,7 +4764,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Hyalu-Cica Sleeping Pack [30m</t>
+          <t>SKIN1004 - Madagascar Centella Hyalu-Cica Sleeping Pack</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4806,7 +4784,7 @@
         <v>6</v>
       </c>
       <c r="I106">
-        <f>H106*$L$1</f>
+        <f>H106*$N$1</f>
         <v/>
       </c>
       <c r="J106">
@@ -4827,7 +4805,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cleansing Bar [106g</t>
+          <t xml:space="preserve">SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cleansing Bar </t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4844,10 +4822,10 @@
         <v/>
       </c>
       <c r="H107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I107">
-        <f>H107*$L$1</f>
+        <f>H107*$N$1</f>
         <v/>
       </c>
       <c r="J107">
@@ -4868,7 +4846,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Argireline Solution 10% [30ml] / Сыворотка дл</t>
+          <t>THE ORDINARY - Argireline Solution 10% [30ml] / Сыворот</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4885,10 +4863,10 @@
         <v/>
       </c>
       <c r="H108" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I108">
-        <f>H108*$L$1</f>
+        <f>H108*$N$1</f>
         <v/>
       </c>
       <c r="J108">
@@ -4909,7 +4887,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [240ml</t>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution [KOR] [</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4926,10 +4904,10 @@
         <v/>
       </c>
       <c r="H109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I109">
-        <f>H109*$L$1</f>
+        <f>H109*$N$1</f>
         <v/>
       </c>
       <c r="J109">
@@ -4967,10 +4945,10 @@
         <v/>
       </c>
       <c r="H110" t="n">
-        <v>3569</v>
+        <v>3149</v>
       </c>
       <c r="I110">
-        <f>H110*$L$1</f>
+        <f>H110*$N$1</f>
         <v/>
       </c>
       <c r="J110">
@@ -4991,7 +4969,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыво</t>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -5008,10 +4986,10 @@
         <v/>
       </c>
       <c r="H111" t="n">
-        <v>618</v>
+        <v>585</v>
       </c>
       <c r="I111">
-        <f>H111*$L$1</f>
+        <f>H111*$N$1</f>
         <v/>
       </c>
       <c r="J111">
@@ -5032,7 +5010,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / 60pad</t>
+          <t xml:space="preserve">CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / </t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -5049,10 +5027,10 @@
         <v/>
       </c>
       <c r="H112" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="I112">
-        <f>H112*$L$1</f>
+        <f>H112*$N$1</f>
         <v/>
       </c>
       <c r="J112">
@@ -5073,7 +5051,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15ml]/По</t>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15m</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -5090,10 +5068,10 @@
         <v/>
       </c>
       <c r="H113" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I113">
-        <f>H113*$L$1</f>
+        <f>H113*$N$1</f>
         <v/>
       </c>
       <c r="J113">
@@ -5114,7 +5092,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]/Тоне</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -5131,10 +5109,10 @@
         <v/>
       </c>
       <c r="H114" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I114">
-        <f>H114*$L$1</f>
+        <f>H114*$N$1</f>
         <v/>
       </c>
       <c r="J114">
@@ -5155,7 +5133,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/Восст</t>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]/</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -5172,10 +5150,10 @@
         <v/>
       </c>
       <c r="H115" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I115">
-        <f>H115*$L$1</f>
+        <f>H115*$N$1</f>
         <v/>
       </c>
       <c r="J115">
@@ -5196,7 +5174,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30ml]/ус</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30m</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -5213,10 +5191,10 @@
         <v/>
       </c>
       <c r="H116" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I116">
-        <f>H116*$L$1</f>
+        <f>H116*$N$1</f>
         <v/>
       </c>
       <c r="J116">
@@ -5237,7 +5215,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_10ml [10ml]/Сыворот</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_10ml [10ml]/Сы</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -5254,10 +5232,10 @@
         <v/>
       </c>
       <c r="H117" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I117">
-        <f>H117*$L$1</f>
+        <f>H117*$N$1</f>
         <v/>
       </c>
       <c r="J117">
@@ -5278,7 +5256,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем для вос</t>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]/Крем дл</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -5295,10 +5273,10 @@
         <v/>
       </c>
       <c r="H118" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I118">
-        <f>H118*$L$1</f>
+        <f>H118*$N$1</f>
         <v/>
       </c>
       <c r="J118">
@@ -5319,7 +5297,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]/Крем для выр</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]/Крем дл</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -5336,10 +5314,10 @@
         <v/>
       </c>
       <c r="H119" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I119">
-        <f>H119*$L$1</f>
+        <f>H119*$N$1</f>
         <v/>
       </c>
       <c r="J119">
@@ -5355,19 +5333,19 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>551616449</t>
+          <t>551482493</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI STARTER KIT (NEW) [30ml+10ml+10ml]/Вос</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сы</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>14</v>
+        <v>234</v>
       </c>
       <c r="E120" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -5377,10 +5355,10 @@
         <v/>
       </c>
       <c r="H120" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I120">
-        <f>H120*$L$1</f>
+        <f>H120*$N$1</f>
         <v/>
       </c>
       <c r="J120">
@@ -5396,19 +5374,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>551482493</t>
+          <t>551616449</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]/Сыворот</t>
+          <t>CELIMAX THE REAL NONI STARTER KIT (NEW) [30ml+10ml+10ml</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>234</v>
+        <v>14</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -5421,7 +5399,7 @@
         <v>5</v>
       </c>
       <c r="I121">
-        <f>H121*$L$1</f>
+        <f>H121*$N$1</f>
         <v/>
       </c>
       <c r="J121">
@@ -5442,7 +5420,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [150ml]</t>
+          <t>CELIMAX THE REAL NONI MOISTURE BALANCING TONER (NEW) [1</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -5462,7 +5440,7 @@
         <v>2</v>
       </c>
       <c r="I122">
-        <f>H122*$L$1</f>
+        <f>H122*$N$1</f>
         <v/>
       </c>
       <c r="J122">
@@ -5483,7 +5461,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CELIMAX DUAL BARRIER TRIAL KIT [20ml+10ml]/набор для восстан</t>
+          <t>CELIMAX DUAL BARRIER TRIAL KIT [20ml+10ml]/набор для во</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -5503,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="I123">
-        <f>H123*$L$1</f>
+        <f>H123*$N$1</f>
         <v/>
       </c>
       <c r="J123">
@@ -5524,7 +5502,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДРН</t>
+          <t>VT PDRN ESSENCE 100 / Укрепляющая бустер-эссенция с ПДР</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -5544,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="I124">
-        <f>H124*$L$1</f>
+        <f>H124*$N$1</f>
         <v/>
       </c>
       <c r="J124">
@@ -5585,7 +5563,7 @@
         <v>0</v>
       </c>
       <c r="I125">
-        <f>H125*$L$1</f>
+        <f>H125*$N$1</f>
         <v/>
       </c>
       <c r="J125">
@@ -5596,19 +5574,20 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SKIN1004 Madagascar Centella Ampoule 55ml</t>
+          <t>Осветляющий Крем от пигментации с Транексамовой Кислото</t>
         </is>
       </c>
       <c r="D126" t="n">
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>1500</v>
+        <v>1344</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -5621,7 +5600,7 @@
         <v>0</v>
       </c>
       <c r="I126">
-        <f>H126*$L$1</f>
+        <f>H126*$N$1</f>
         <v/>
       </c>
       <c r="J126">
@@ -5632,19 +5611,20 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Пенка для умыванияCELIMAX THE REAL NONI ACNE BUBBLE CLEANSER</t>
+          <t>Сыворотка для лица от морщин с микроиглами 7500 и пдрн/</t>
         </is>
       </c>
       <c r="D127" t="n">
         <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>312</v>
+        <v>400</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -5657,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="I127">
-        <f>H127*$L$1</f>
+        <f>H127*$N$1</f>
         <v/>
       </c>
       <c r="J127">
@@ -5668,19 +5648,20 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Сыворотка-лифтинг с ПДРН и пептидами Medicube, 30 мл/PDRN PI</t>
+          <t>Гель для душа от прыщей с кислотами/PINE CALMING CICA B</t>
         </is>
       </c>
       <c r="D128" t="n">
         <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -5693,7 +5674,7 @@
         <v>0</v>
       </c>
       <c r="I128">
-        <f>H128*$L$1</f>
+        <f>H128*$N$1</f>
         <v/>
       </c>
       <c r="J128">
@@ -5704,9 +5685,10 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
           <t xml:space="preserve">1025 DOKDO BUBBLE FOAM_150ml (дозатор ) </t>
@@ -5729,7 +5711,7 @@
         <v>0</v>
       </c>
       <c r="I129">
-        <f>H129*$L$1</f>
+        <f>H129*$N$1</f>
         <v/>
       </c>
       <c r="J129">
@@ -5740,9 +5722,10 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
           <t>Блеск Плампер для губ VT REEDLE SHOT LIP PLUMPER EXPERT</t>
@@ -5765,7 +5748,7 @@
         <v>0</v>
       </c>
       <c r="I130">
-        <f>H130*$L$1</f>
+        <f>H130*$N$1</f>
         <v/>
       </c>
       <c r="J130">
@@ -5776,19 +5759,20 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Гель для душа от прыщей с кислотами/PINE CALMING CICA BODY W</t>
+          <t>CELIMAX THE REAL NONI REFRESH CLAY MASK 120G</t>
         </is>
       </c>
       <c r="D131" t="n">
         <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -5801,7 +5785,7 @@
         <v>0</v>
       </c>
       <c r="I131">
-        <f>H131*$L$1</f>
+        <f>H131*$N$1</f>
         <v/>
       </c>
       <c r="J131">
@@ -5812,19 +5796,20 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сыворотка для лица от морщин с микроиглами 7500 и пдрн/PDRN </t>
+          <t xml:space="preserve">CELIMAX DUAL BARRIER MILD GEL CLEANSER 200ML(дозатор) </t>
         </is>
       </c>
       <c r="D132" t="n">
         <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>400</v>
+        <v>288</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -5837,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="I132">
-        <f>H132*$L$1</f>
+        <f>H132*$N$1</f>
         <v/>
       </c>
       <c r="J132">
@@ -5848,19 +5833,20 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Осветляющий Крем от пигментации с Транексамовой Кислотой/[De</t>
+          <t>Тонер  для лица увлажняющий от прыщей Корея/EXOSOME CIC</t>
         </is>
       </c>
       <c r="D133" t="n">
         <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>1344</v>
+        <v>240</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -5873,7 +5859,7 @@
         <v>0</v>
       </c>
       <c r="I133">
-        <f>H133*$L$1</f>
+        <f>H133*$N$1</f>
         <v/>
       </c>
       <c r="J133">
@@ -5884,19 +5870,20 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml]</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING KIT</t>
         </is>
       </c>
       <c r="D134" t="n">
         <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>2000</v>
+        <v>576</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
@@ -5909,7 +5896,7 @@
         <v>0</v>
       </c>
       <c r="I134">
-        <f>H134*$L$1</f>
+        <f>H134*$N$1</f>
         <v/>
       </c>
       <c r="J134">
@@ -5920,19 +5907,20 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Увлажняющий тонер-эссенция для лица с аденозином 7500 ppm/Ad</t>
+          <t>BIFIDA BIOME AMPOULE TONER 210 мл</t>
         </is>
       </c>
       <c r="D135" t="n">
         <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
@@ -5945,7 +5933,7 @@
         <v>0</v>
       </c>
       <c r="I135">
-        <f>H135*$L$1</f>
+        <f>H135*$N$1</f>
         <v/>
       </c>
       <c r="J135">
@@ -5956,19 +5944,20 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">CELIMAX DUAL BARRIER MILD GEL CLEANSER 200ML(дозатор) </t>
+          <t>SKIN1004 Madagascar Centella Soothing Cream 75ml</t>
         </is>
       </c>
       <c r="D136" t="n">
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>288</v>
+        <v>920</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
@@ -5981,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="I136">
-        <f>H136*$L$1</f>
+        <f>H136*$N$1</f>
         <v/>
       </c>
       <c r="J136">
@@ -5992,9 +5981,10 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
           <t>CELIMAX OIL CONTROL MOISTURIZING CREAM 80ML</t>
@@ -6017,7 +6007,7 @@
         <v>0</v>
       </c>
       <c r="I137">
-        <f>H137*$L$1</f>
+        <f>H137*$N$1</f>
         <v/>
       </c>
       <c r="J137">
@@ -6028,9 +6018,10 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
           <t xml:space="preserve">Сыворотка с пептидами Матриксил 15% от морщин/ </t>
@@ -6053,7 +6044,7 @@
         <v>0</v>
       </c>
       <c r="I138">
-        <f>H138*$L$1</f>
+        <f>H138*$N$1</f>
         <v/>
       </c>
       <c r="J138">
@@ -6064,19 +6055,20 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SKIN1004 Madagascar Centella Soothing Cream 75ml</t>
+          <t>Увлажняющий тонер-эссенция для лица с аденозином 7500 p</t>
         </is>
       </c>
       <c r="D139" t="n">
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>920</v>
+        <v>400</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -6089,7 +6081,7 @@
         <v>0</v>
       </c>
       <c r="I139">
-        <f>H139*$L$1</f>
+        <f>H139*$N$1</f>
         <v/>
       </c>
       <c r="J139">
@@ -6100,19 +6092,20 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BIFIDA BIOME AMPOULE TONER 210 мл</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [1000ml</t>
         </is>
       </c>
       <c r="D140" t="n">
         <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -6125,7 +6118,7 @@
         <v>0</v>
       </c>
       <c r="I140">
-        <f>H140*$L$1</f>
+        <f>H140*$N$1</f>
         <v/>
       </c>
       <c r="J140">
@@ -6136,19 +6129,20 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING KIT</t>
+          <t>Пенка для умыванияCELIMAX THE REAL NONI ACNE BUBBLE CLE</t>
         </is>
       </c>
       <c r="D141" t="n">
         <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>576</v>
+        <v>312</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -6161,7 +6155,7 @@
         <v>0</v>
       </c>
       <c r="I141">
-        <f>H141*$L$1</f>
+        <f>H141*$N$1</f>
         <v/>
       </c>
       <c r="J141">
@@ -6172,19 +6166,20 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Тонер  для лица увлажняющий от прыщей Корея/EXOSOME CICA TON</t>
+          <t>Сыворотка-лифтинг с ПДРН и пептидами Medicube, 30 мл/PD</t>
         </is>
       </c>
       <c r="D142" t="n">
         <v>0</v>
       </c>
       <c r="E142" t="n">
-        <v>240</v>
+        <v>320</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -6197,7 +6192,7 @@
         <v>0</v>
       </c>
       <c r="I142">
-        <f>H142*$L$1</f>
+        <f>H142*$N$1</f>
         <v/>
       </c>
       <c r="J142">
@@ -6208,19 +6203,20 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI REFRESH CLAY MASK 120G</t>
+          <t>SKIN1004 Madagascar Centella Ampoule 55ml</t>
         </is>
       </c>
       <c r="D143" t="n">
         <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>408</v>
+        <v>1500</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -6233,7 +6229,7 @@
         <v>0</v>
       </c>
       <c r="I143">
-        <f>H143*$L$1</f>
+        <f>H143*$N$1</f>
         <v/>
       </c>
       <c r="J143">
@@ -6244,19 +6240,20 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI CALMING GLOW PAD 50PADS,</t>
+          <t>Пенка очищающая для лица от прыщей с сосной и кислотами</t>
         </is>
       </c>
       <c r="D144" t="n">
         <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>984</v>
+        <v>600</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
@@ -6269,7 +6266,7 @@
         <v>0</v>
       </c>
       <c r="I144">
-        <f>H144*$L$1</f>
+        <f>H144*$N$1</f>
         <v/>
       </c>
       <c r="J144">
@@ -6280,19 +6277,20 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>VT REEDLE SHOT LIFTING EYE CREAM</t>
+          <t>1025 DOKDO CREAM_80ml</t>
         </is>
       </c>
       <c r="D145" t="n">
         <v>0</v>
       </c>
       <c r="E145" t="n">
-        <v>1056</v>
+        <v>160</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
@@ -6305,7 +6303,7 @@
         <v>0</v>
       </c>
       <c r="I145">
-        <f>H145*$L$1</f>
+        <f>H145*$N$1</f>
         <v/>
       </c>
       <c r="J145">
@@ -6316,19 +6314,20 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CELIMAX DERMA NATURE GLUTATHIONE LONGLASTING TONE-UP CREAM 3</t>
+          <t>CELIMAX THE REAL NONI CALMING GLOW PAD 50PADS,</t>
         </is>
       </c>
       <c r="D146" t="n">
         <v>0</v>
       </c>
       <c r="E146" t="n">
-        <v>468</v>
+        <v>984</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
@@ -6341,7 +6340,7 @@
         <v>0</v>
       </c>
       <c r="I146">
-        <f>H146*$L$1</f>
+        <f>H146*$N$1</f>
         <v/>
       </c>
       <c r="J146">
@@ -6352,19 +6351,20 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крем для лица увлажняющий для проблемной кожи с сосной/PINE </t>
+          <t>VT REEDLE SHOT LIFTING EYE CREAM</t>
         </is>
       </c>
       <c r="D147" t="n">
         <v>0</v>
       </c>
       <c r="E147" t="n">
-        <v>240</v>
+        <v>1056</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -6377,7 +6377,7 @@
         <v>0</v>
       </c>
       <c r="I147">
-        <f>H147*$L$1</f>
+        <f>H147*$N$1</f>
         <v/>
       </c>
       <c r="J147">
@@ -6388,19 +6388,20 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - ARGAN SILKY MOISTURE</t>
+          <t>Сыворотка для лица от морщин с микроиглами 2000 и пдрн/</t>
         </is>
       </c>
       <c r="D148" t="n">
         <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -6413,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="I148">
-        <f>H148*$L$1</f>
+        <f>H148*$N$1</f>
         <v/>
       </c>
       <c r="J148">
@@ -6424,19 +6425,20 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA ACNE FOAM CLEANSING 150ML</t>
+          <t xml:space="preserve">CELIMAX DERMA NATURE RELIEF MADECICA PH BALANCING FOAM </t>
         </is>
       </c>
       <c r="D149" t="n">
         <v>0</v>
       </c>
       <c r="E149" t="n">
-        <v>480</v>
+        <v>320</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
@@ -6449,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="I149">
-        <f>H149*$L$1</f>
+        <f>H149*$N$1</f>
         <v/>
       </c>
       <c r="J149">
@@ -6460,19 +6462,20 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Крем для лица c Бакучиолом и Микроиглами от морщин/ Bakuchio</t>
+          <t xml:space="preserve">Интенсивная антивозрастная сыворотка для лица PDRN 4%, </t>
         </is>
       </c>
       <c r="D150" t="n">
         <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>480</v>
+        <v>1530</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
@@ -6485,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="I150">
-        <f>H150*$L$1</f>
+        <f>H150*$N$1</f>
         <v/>
       </c>
       <c r="J150">
@@ -6496,12 +6499,13 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL CICA SOOTHING CREAM 50ML</t>
+          <t>Сыворотка для лица осветляющая от пигментации/[Derma Fa</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -6521,7 +6525,7 @@
         <v>0</v>
       </c>
       <c r="I151">
-        <f>H151*$L$1</f>
+        <f>H151*$N$1</f>
         <v/>
       </c>
       <c r="J151">
@@ -6532,19 +6536,20 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Крем для лица укрепляющий с ретиналем 300ppm/[Derma Factory]</t>
+          <t>SOYBEAN SERUM_50ml/Сыворотка для лица увлажняющая от мо</t>
         </is>
       </c>
       <c r="D152" t="n">
         <v>0</v>
       </c>
       <c r="E152" t="n">
-        <v>1248</v>
+        <v>210</v>
       </c>
       <c r="F152" t="n">
         <v>0</v>
@@ -6557,7 +6562,7 @@
         <v>0</v>
       </c>
       <c r="I152">
-        <f>H152*$L$1</f>
+        <f>H152*$N$1</f>
         <v/>
       </c>
       <c r="J152">
@@ -6568,19 +6573,20 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Интенсивная антивозрастная сыворотка для лица PDRN 4%, 30 мл</t>
+          <t>CELIMAX OIL CONTROL CAPSULE ESSENCE 30ML</t>
         </is>
       </c>
       <c r="D153" t="n">
         <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>1530</v>
+        <v>420</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
@@ -6593,7 +6599,7 @@
         <v>0</v>
       </c>
       <c r="I153">
-        <f>H153*$L$1</f>
+        <f>H153*$N$1</f>
         <v/>
       </c>
       <c r="J153">
@@ -6604,19 +6610,20 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Сыворотка для лица осветляющая от пигментации/[Derma Factory</t>
+          <t>ROUND LAB CAMELLIA DEEP COLLAGEN FIRMING CREAM_50ml</t>
         </is>
       </c>
       <c r="D154" t="n">
         <v>0</v>
       </c>
       <c r="E154" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -6629,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="I154">
-        <f>H154*$L$1</f>
+        <f>H154*$N$1</f>
         <v/>
       </c>
       <c r="J154">
@@ -6640,19 +6647,20 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CELIMAX DERMA NATURE RELIEF MADECICA PH BALANCING FOAM CLEAN</t>
+          <t>CELIMAX JI WOO GAE ONE STEP MILD CLEANSING PAD 60PADS</t>
         </is>
       </c>
       <c r="D155" t="n">
         <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="F155" t="n">
         <v>0</v>
@@ -6665,7 +6673,7 @@
         <v>0</v>
       </c>
       <c r="I155">
-        <f>H155*$L$1</f>
+        <f>H155*$N$1</f>
         <v/>
       </c>
       <c r="J155">
@@ -6676,19 +6684,20 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOYBEAN SERUM_50ml/Сыворотка для лица увлажняющая от морщин </t>
+          <t>CELIMAX THE REAL CICA NIACINAMIDE AC CALMING SERUM 40ML</t>
         </is>
       </c>
       <c r="D156" t="n">
         <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>210</v>
+        <v>864</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
@@ -6701,7 +6710,7 @@
         <v>0</v>
       </c>
       <c r="I156">
-        <f>H156*$L$1</f>
+        <f>H156*$N$1</f>
         <v/>
       </c>
       <c r="J156">
@@ -6712,19 +6721,20 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE ONE STEP MILD CLEANSING PAD 60PADS</t>
+          <t>Крем для лица c Бакучиолом и Микроиглами от морщин/ Bak</t>
         </is>
       </c>
       <c r="D157" t="n">
         <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>352</v>
+        <v>480</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
@@ -6737,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="I157">
-        <f>H157*$L$1</f>
+        <f>H157*$N$1</f>
         <v/>
       </c>
       <c r="J157">
@@ -6748,19 +6758,20 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ROUND LAB CAMELLIA DEEP COLLAGEN FIRMING CREAM_50ml</t>
+          <t>CELIMAX JI WOO GAE CICA BHA ACNE FOAM CLEANSING 150ML</t>
         </is>
       </c>
       <c r="D158" t="n">
         <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>400</v>
+        <v>480</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
@@ -6773,7 +6784,7 @@
         <v>0</v>
       </c>
       <c r="I158">
-        <f>H158*$L$1</f>
+        <f>H158*$N$1</f>
         <v/>
       </c>
       <c r="J158">
@@ -6784,19 +6795,20 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CELIMAX OIL CONTROL CAPSULE ESSENCE 30ML</t>
+          <t>CELIMAX THE REAL CICA SOOTHING CREAM 50ML</t>
         </is>
       </c>
       <c r="D159" t="n">
         <v>0</v>
       </c>
       <c r="E159" t="n">
-        <v>420</v>
+        <v>1200</v>
       </c>
       <c r="F159" t="n">
         <v>0</v>
@@ -6809,7 +6821,7 @@
         <v>0</v>
       </c>
       <c r="I159">
-        <f>H159*$L$1</f>
+        <f>H159*$N$1</f>
         <v/>
       </c>
       <c r="J159">
@@ -6820,19 +6832,20 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL CICA NIACINAMIDE AC CALMING SERUM 40ML</t>
+          <t>Крем для лица укрепляющий с ретиналем 300ppm/[Derma Fac</t>
         </is>
       </c>
       <c r="D160" t="n">
         <v>0</v>
       </c>
       <c r="E160" t="n">
-        <v>864</v>
+        <v>1248</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
@@ -6845,7 +6858,7 @@
         <v>0</v>
       </c>
       <c r="I160">
-        <f>H160*$L$1</f>
+        <f>H160*$N$1</f>
         <v/>
       </c>
       <c r="J160">
@@ -6856,19 +6869,20 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Пенка очищающая для лица от прыщей с сосной и кислотами/PINE</t>
+          <t>Крем для лица увлажняющий для проблемной кожи с сосной/</t>
         </is>
       </c>
       <c r="D161" t="n">
         <v>0</v>
       </c>
       <c r="E161" t="n">
-        <v>600</v>
+        <v>240</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -6881,7 +6895,7 @@
         <v>0</v>
       </c>
       <c r="I161">
-        <f>H161*$L$1</f>
+        <f>H161*$N$1</f>
         <v/>
       </c>
       <c r="J161">
@@ -6892,19 +6906,20 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr">
         <is>
-          <t>1025 DOKDO CREAM_80ml</t>
+          <t>DEOPROCE SHAMPOO - ARGAN SILKY MOISTURE</t>
         </is>
       </c>
       <c r="D162" t="n">
         <v>0</v>
       </c>
       <c r="E162" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="F162" t="n">
         <v>0</v>
@@ -6917,7 +6932,7 @@
         <v>0</v>
       </c>
       <c r="I162">
-        <f>H162*$L$1</f>
+        <f>H162*$N$1</f>
         <v/>
       </c>
       <c r="J162">
@@ -6928,19 +6943,20 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сыворотка для лица от морщин с микроиглами 2000 и пдрн/PDRN </t>
+          <t>CELIMAX DERMA NATURE GLUTATHIONE LONGLASTING TONE-UP CR</t>
         </is>
       </c>
       <c r="D163" t="n">
         <v>0</v>
       </c>
       <c r="E163" t="n">
-        <v>300</v>
+        <v>468</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
@@ -6953,7 +6969,7 @@
         <v>0</v>
       </c>
       <c r="I163">
-        <f>H163*$L$1</f>
+        <f>H163*$N$1</f>
         <v/>
       </c>
       <c r="J163">
@@ -6964,19 +6980,20 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Крем для лица увлажняющий капсульный /PDRN PINK COLLAGEN CAP</t>
+          <t>капсульный крем для лица /TXA NIACINAMIDE CAPSULE CREAM</t>
         </is>
       </c>
       <c r="D164" t="n">
         <v>0</v>
       </c>
       <c r="E164" t="n">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
@@ -6989,7 +7006,7 @@
         <v>0</v>
       </c>
       <c r="I164">
-        <f>H164*$L$1</f>
+        <f>H164*$N$1</f>
         <v/>
       </c>
       <c r="J164">
@@ -7000,19 +7017,20 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>капсульный крем для лица /TXA NIACINAMIDE CAPSULE CREAM 55g</t>
+          <t>CELIMAX ONE STEP BODY BRIGHTENING PAD 60PADS</t>
         </is>
       </c>
       <c r="D165" t="n">
         <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>240</v>
+        <v>528</v>
       </c>
       <c r="F165" t="n">
         <v>0</v>
@@ -7025,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="I165">
-        <f>H165*$L$1</f>
+        <f>H165*$N$1</f>
         <v/>
       </c>
       <c r="J165">
@@ -7036,12 +7054,13 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ROUND LAB STICK POUCH KIT(Набор саше миниатюр для лица 12 шт</t>
+          <t xml:space="preserve">ROUND LAB STICK POUCH KIT(Набор саше миниатюр для лица </t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -7061,7 +7080,7 @@
         <v>0</v>
       </c>
       <c r="I166">
-        <f>H166*$L$1</f>
+        <f>H166*$N$1</f>
         <v/>
       </c>
       <c r="J166">
@@ -7072,19 +7091,20 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
-          <t>CELIMAX ONE STEP BODY BRIGHTENING PAD 60PADS</t>
+          <t>Крем для лица увлажняющий капсульный /PDRN PINK COLLAGE</t>
         </is>
       </c>
       <c r="D167" t="n">
         <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>528</v>
+        <v>160</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
@@ -7097,7 +7117,7 @@
         <v>0</v>
       </c>
       <c r="I167">
-        <f>H167*$L$1</f>
+        <f>H167*$N$1</f>
         <v/>
       </c>
       <c r="J167">
@@ -7108,19 +7128,20 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SKIN1004 Madagascar Centella Tone Brightening Capsule Ampoul</t>
+          <t>PDRN PINK HYALURONIC MOISTURIZING CREAM 50ml</t>
         </is>
       </c>
       <c r="D168" t="n">
         <v>0</v>
       </c>
       <c r="E168" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -7133,7 +7154,7 @@
         <v>0</v>
       </c>
       <c r="I168">
-        <f>H168*$L$1</f>
+        <f>H168*$N$1</f>
         <v/>
       </c>
       <c r="J168">
@@ -7144,19 +7165,20 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI ENERGY REPAIR CREAM 50ML</t>
+          <t>Антивозрастная сыворотка-стик для лица с волюфилином</t>
         </is>
       </c>
       <c r="D169" t="n">
         <v>0</v>
       </c>
       <c r="E169" t="n">
-        <v>720</v>
+        <v>1053</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
@@ -7169,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="I169">
-        <f>H169*$L$1</f>
+        <f>H169*$N$1</f>
         <v/>
       </c>
       <c r="J169">
@@ -7180,19 +7202,20 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>PDRN PINK HYALURONIC MOISTURIZING CREAM 50ml</t>
+          <t>SKIN1004 Madagascar Centella Tone Brightening Capsule A</t>
         </is>
       </c>
       <c r="D170" t="n">
         <v>0</v>
       </c>
       <c r="E170" t="n">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="F170" t="n">
         <v>0</v>
@@ -7205,7 +7228,7 @@
         <v>0</v>
       </c>
       <c r="I170">
-        <f>H170*$L$1</f>
+        <f>H170*$N$1</f>
         <v/>
       </c>
       <c r="J170">
@@ -7216,19 +7239,20 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Антивозрастная сыворотка-стик для лица с волюфилином</t>
+          <t>CELIMAX THE REAL NONI ENERGY REPAIR CREAM 50ML</t>
         </is>
       </c>
       <c r="D171" t="n">
         <v>0</v>
       </c>
       <c r="E171" t="n">
-        <v>1053</v>
+        <v>720</v>
       </c>
       <c r="F171" t="n">
         <v>0</v>
@@ -7241,7 +7265,7 @@
         <v>0</v>
       </c>
       <c r="I171">
-        <f>H171*$L$1</f>
+        <f>H171*$N$1</f>
         <v/>
       </c>
       <c r="J171">
@@ -7252,19 +7276,20 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Сыворотка с Ниацинамидом для лица от прыщей Niacinamide/[Der</t>
+          <t>Гидрофильное масло CELIMAX DERMA NATURE FRESH BLACKHEAD</t>
         </is>
       </c>
       <c r="D172" t="n">
         <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>1020</v>
+        <v>315</v>
       </c>
       <c r="F172" t="n">
         <v>0</v>
@@ -7277,7 +7302,7 @@
         <v>0</v>
       </c>
       <c r="I172">
-        <f>H172*$L$1</f>
+        <f>H172*$N$1</f>
         <v/>
       </c>
       <c r="J172">
@@ -7288,12 +7313,13 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PINE CALMING CICA PAD_50pcs/Тонер пэды диски для лица от пры</t>
+          <t>PINE CALMING CICA PAD_50pcs/Тонер пэды диски для лица о</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -7313,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="I173">
-        <f>H173*$L$1</f>
+        <f>H173*$N$1</f>
         <v/>
       </c>
       <c r="J173">
@@ -7324,19 +7350,20 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Гидрофильное масло CELIMAX DERMA NATURE FRESH BLACKHEAD JOJO</t>
+          <t>Сыворотка с Ниацинамидом для лица от прыщей Niacinamide</t>
         </is>
       </c>
       <c r="D174" t="n">
         <v>0</v>
       </c>
       <c r="E174" t="n">
-        <v>315</v>
+        <v>1020</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
@@ -7349,7 +7376,7 @@
         <v>0</v>
       </c>
       <c r="I174">
-        <f>H174*$L$1</f>
+        <f>H174*$N$1</f>
         <v/>
       </c>
       <c r="J174">
@@ -7360,12 +7387,13 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>НОВЫЕ/ПРОЧЕЕ</t>
-        </is>
-      </c>
+          <t>НОВЫЕ</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Тонер пэды для лица,60 шт CELIMAX JI WOO GAE HEARTLEAF BHA P</t>
+          <t xml:space="preserve">Тонер пэды для лица,60 шт CELIMAX JI WOO GAE HEARTLEAF </t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -7385,7 +7413,7 @@
         <v>0</v>
       </c>
       <c r="I175">
-        <f>H175*$L$1</f>
+        <f>H175*$N$1</f>
         <v/>
       </c>
       <c r="J175">
@@ -7405,1779 +7433,4 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Бренд</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Название</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>Баркод</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>кол-во</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>сумма</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>в коробе</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>Объем короба</t>
-        </is>
-      </c>
-      <c r="I1" s="6" t="inlineStr">
-        <is>
-          <t>Вес короба кг</t>
-        </is>
-      </c>
-      <c r="J1" s="6" t="inlineStr">
-        <is>
-          <t>Коробок в заказ</t>
-        </is>
-      </c>
-      <c r="K1" s="6" t="inlineStr">
-        <is>
-          <t>Объем</t>
-        </is>
-      </c>
-      <c r="L1" s="6" t="inlineStr">
-        <is>
-          <t>Вес кг</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CELIMAX</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]/Сыво</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>8809700320805</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1266</v>
-      </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2">
-        <f>D2*E2</f>
-        <v/>
-      </c>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2">
-        <f>IF(G2="","",ROUNDUP(D2/G2,0))</f>
-        <v/>
-      </c>
-      <c r="K2">
-        <f>IF(J2="","",J2*H2)</f>
-        <v/>
-      </c>
-      <c r="L2">
-        <f>IF(J2="","",J2*I2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ENOUGH - Collagen 3in1 Sun Cream SPF50 PA+++ [50ml] / отбели</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>8809755462130</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>5018</v>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3">
-        <f>D3*E3</f>
-        <v/>
-      </c>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3">
-        <f>IF(G3="","",ROUNDUP(D3/G3,0))</f>
-        <v/>
-      </c>
-      <c r="K3">
-        <f>IF(J3="","",J3*H3)</f>
-        <v/>
-      </c>
-      <c r="L3">
-        <f>IF(J3="","",J3*I3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13] / Тональны</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>8809474498809</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1990</v>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4">
-        <f>D4*E4</f>
-        <v/>
-      </c>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4">
-        <f>IF(G4="","",ROUNDUP(D4/G4,0))</f>
-        <v/>
-      </c>
-      <c r="K4">
-        <f>IF(J4="","",J4*H4)</f>
-        <v/>
-      </c>
-      <c r="L4">
-        <f>IF(J4="","",J4*I4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MANYO</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MANYO - Galac Whitening Vita Serum [50ml] / Осветляющая сыво</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>8809730952014</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1204</v>
-      </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5">
-        <f>D5*E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5">
-        <f>IF(G5="","",ROUNDUP(D5/G5,0))</f>
-        <v/>
-      </c>
-      <c r="K5">
-        <f>IF(J5="","",J5*H5)</f>
-        <v/>
-      </c>
-      <c r="L5">
-        <f>IF(J5="","",J5*I5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>JIGOTT</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml] / Крем для лица увлажн</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>8809210036517</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>562</v>
-      </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6">
-        <f>D6*E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6">
-        <f>IF(G6="","",ROUNDUP(D6/G6,0))</f>
-        <v/>
-      </c>
-      <c r="K6">
-        <f>IF(J6="","",J6*H6)</f>
-        <v/>
-      </c>
-      <c r="L6">
-        <f>IF(J6="","",J6*I6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [60ea] / Ги</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>8809239801820</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>643</v>
-      </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7">
-        <f>D7*E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7">
-        <f>IF(G7="","",ROUNDUP(D7/G7,0))</f>
-        <v/>
-      </c>
-      <c r="K7">
-        <f>IF(J7="","",J7*H7)</f>
-        <v/>
-      </c>
-      <c r="L7">
-        <f>IF(J7="","",J7*I7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21] / Тональны</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>8809474498816</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1048</v>
-      </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8">
-        <f>D8*E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8">
-        <f>IF(G8="","",ROUNDUP(D8/G8,0))</f>
-        <v/>
-      </c>
-      <c r="K8">
-        <f>IF(J8="","",J8*H8)</f>
-        <v/>
-      </c>
-      <c r="L8">
-        <f>IF(J8="","",J8*I8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA - Aqua Hyaluronic Acid Water Drop Cream / Увлажня</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>8809418750505</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>1651</v>
-      </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9">
-        <f>D9*E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9">
-        <f>IF(G9="","",ROUNDUP(D9/G9,0))</f>
-        <v/>
-      </c>
-      <c r="K9">
-        <f>IF(J9="","",J9*H9)</f>
-        <v/>
-      </c>
-      <c r="L9">
-        <f>IF(J9="","",J9*I9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ENOUGH - Premium 8 Peptide Full Cover Perfect Foundation [To</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>8809605870979</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>955</v>
-      </c>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10">
-        <f>D10*E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10">
-        <f>IF(G10="","",ROUNDUP(D10/G10,0))</f>
-        <v/>
-      </c>
-      <c r="K10">
-        <f>IF(J10="","",J10*H10)</f>
-        <v/>
-      </c>
-      <c r="L10">
-        <f>IF(J10="","",J10*I10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs] / Охлажда</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>8809508850443</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>321</v>
-      </c>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11">
-        <f>D11*E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11">
-        <f>IF(G11="","",ROUNDUP(D11/G11,0))</f>
-        <v/>
-      </c>
-      <c r="K11">
-        <f>IF(J11="","",J11*H11)</f>
-        <v/>
-      </c>
-      <c r="L11">
-        <f>IF(J11="","",J11*I11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundation [</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>8809605871938</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>749</v>
-      </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12">
-        <f>D12*E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12">
-        <f>IF(G12="","",ROUNDUP(D12/G12,0))</f>
-        <v/>
-      </c>
-      <c r="K12">
-        <f>IF(J12="","",J12*H12)</f>
-        <v/>
-      </c>
-      <c r="L12">
-        <f>IF(J12="","",J12*I12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ENOUGH - Premium Ultra X10 Cover Up Collagen Foundation [Ton</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>8809605870993</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>333</v>
-      </c>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13">
-        <f>D13*E13</f>
-        <v/>
-      </c>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13">
-        <f>IF(G13="","",ROUNDUP(D13/G13,0))</f>
-        <v/>
-      </c>
-      <c r="K13">
-        <f>IF(J13="","",J13*H13)</f>
-        <v/>
-      </c>
-      <c r="L13">
-        <f>IF(J13="","",J13*I13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ENOUGH - Premium Rich Gold Double Wear Radiance Foundation [</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>8809605871945</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>698</v>
-      </c>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14">
-        <f>D14*E14</f>
-        <v/>
-      </c>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14">
-        <f>IF(G14="","",ROUNDUP(D14/G14,0))</f>
-        <v/>
-      </c>
-      <c r="K14">
-        <f>IF(J14="","",J14*H14)</f>
-        <v/>
-      </c>
-      <c r="L14">
-        <f>IF(J14="","",J14*I14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA - Natural 90% Olive Cleansing Oil / Очищающее гид</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>8809071365504</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1203</v>
-      </c>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15">
-        <f>D15*E15</f>
-        <v/>
-      </c>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15">
-        <f>IF(G15="","",ROUNDUP(D15/G15,0))</f>
-        <v/>
-      </c>
-      <c r="K15">
-        <f>IF(J15="","",J15*H15)</f>
-        <v/>
-      </c>
-      <c r="L15">
-        <f>IF(J15="","",J15*I15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MANYO</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>MANYO - Bifida Biome Ampoule Toner [400ml] / Ампульный укреп</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>8809657114137</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1111</v>
-      </c>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16">
-        <f>D16*E16</f>
-        <v/>
-      </c>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16">
-        <f>IF(G16="","",ROUNDUP(D16/G16,0))</f>
-        <v/>
-      </c>
-      <c r="K16">
-        <f>IF(J16="","",J16*H16)</f>
-        <v/>
-      </c>
-      <c r="L16">
-        <f>IF(J16="","",J16*I16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>MANYO</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MANYO - Pure Cleansing Oil [200ml] / Гидрофильное масло для </t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>8809082392292</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>678</v>
-      </c>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17">
-        <f>D17*E17</f>
-        <v/>
-      </c>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17">
-        <f>IF(G17="","",ROUNDUP(D17/G17,0))</f>
-        <v/>
-      </c>
-      <c r="K17">
-        <f>IF(J17="","",J17*H17)</f>
-        <v/>
-      </c>
-      <c r="L17">
-        <f>IF(J17="","",J17*I17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA - Hell pore clean up aha fruit toner [ 200ml] / П</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>8809339907910</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>578</v>
-      </c>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18">
-        <f>D18*E18</f>
-        <v/>
-      </c>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18">
-        <f>IF(G18="","",ROUNDUP(D18/G18,0))</f>
-        <v/>
-      </c>
-      <c r="K18">
-        <f>IF(J18="","",J18*H18)</f>
-        <v/>
-      </c>
-      <c r="L18">
-        <f>IF(J18="","",J18*I18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>DEOPROCE</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DEOPROCE SHAMPOO+BALSAM - BLACK GARLIC[2000ml]</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="n">
-        <v>374</v>
-      </c>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19">
-        <f>D19*E19</f>
-        <v/>
-      </c>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19">
-        <f>IF(G19="","",ROUNDUP(D19/G19,0))</f>
-        <v/>
-      </c>
-      <c r="K19">
-        <f>IF(J19="","",J19*H19)</f>
-        <v/>
-      </c>
-      <c r="L19">
-        <f>IF(J19="","",J19*I19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ELIZAVECCA - 24K Gold Snail Cleansing Foam [180ml] / Золотая</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>8809418750338</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>896</v>
-      </c>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20">
-        <f>D20*E20</f>
-        <v/>
-      </c>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
-      <c r="J20">
-        <f>IF(G20="","",ROUNDUP(D20/G20,0))</f>
-        <v/>
-      </c>
-      <c r="K20">
-        <f>IF(J20="","",J20*H20)</f>
-        <v/>
-      </c>
-      <c r="L20">
-        <f>IF(J20="","",J20*I20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ENOUGH - Premium Ultra X10 Cover Up Collagen Foundation [Ton</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>8809605871006</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>610</v>
-      </c>
-      <c r="E21" t="n">
-        <v>3880</v>
-      </c>
-      <c r="F21">
-        <f>D21*E21</f>
-        <v/>
-      </c>
-      <c r="G21" t="n">
-        <v>100</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.0314</v>
-      </c>
-      <c r="I21" t="n">
-        <v>15</v>
-      </c>
-      <c r="J21">
-        <f>IF(G21="","",ROUNDUP(D21/G21,0))</f>
-        <v/>
-      </c>
-      <c r="K21">
-        <f>IF(J21="","",J21*H21)</f>
-        <v/>
-      </c>
-      <c r="L21">
-        <f>IF(J21="","",J21*I21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PETITFEE - Chamomile Lightening Hydrogel Mask Pack [5pcs] / </t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>8809508850436</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>745</v>
-      </c>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22">
-        <f>D22*E22</f>
-        <v/>
-      </c>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22">
-        <f>IF(G22="","",ROUNDUP(D22/G22,0))</f>
-        <v/>
-      </c>
-      <c r="K22">
-        <f>IF(J22="","",J22*H22)</f>
-        <v/>
-      </c>
-      <c r="L22">
-        <f>IF(J22="","",J22*I22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>EKEL</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>EKEL - Ampule Сream Сollagen [70ml] / Крем для лица ампульны</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>8809242276820</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>501</v>
-      </c>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23">
-        <f>D23*E23</f>
-        <v/>
-      </c>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
-      <c r="J23">
-        <f>IF(G23="","",ROUNDUP(D23/G23,0))</f>
-        <v/>
-      </c>
-      <c r="K23">
-        <f>IF(J23="","",J23*H23)</f>
-        <v/>
-      </c>
-      <c r="L23">
-        <f>IF(J23="","",J23*I23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ROUND LAB SOYBEAN PANTHENOL CREAM_80ml - Крем для лица с чёр</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>8809875907337</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>406</v>
-      </c>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24">
-        <f>D24*E24</f>
-        <v/>
-      </c>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="n"/>
-      <c r="J24">
-        <f>IF(G24="","",ROUNDUP(D24/G24,0))</f>
-        <v/>
-      </c>
-      <c r="K24">
-        <f>IF(J24="","",J24*H24)</f>
-        <v/>
-      </c>
-      <c r="L24">
-        <f>IF(J24="","",J24*I24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>HEIMISH</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>HEIMISH - All Clean Balm Mandarin [120ml] / Очищающий гидроф</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>8809481761996</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>562</v>
-      </c>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25">
-        <f>D25*E25</f>
-        <v/>
-      </c>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25">
-        <f>IF(G25="","",ROUNDUP(D25/G25,0))</f>
-        <v/>
-      </c>
-      <c r="K25">
-        <f>IF(J25="","",J25*H25)</f>
-        <v/>
-      </c>
-      <c r="L25">
-        <f>IF(J25="","",J25*I25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ETUDEHOUSE</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ETUDE - Baking Powder Crunch Pore Scrub [24*7ml] / Очищающий</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>8809820692707</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>331</v>
-      </c>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26">
-        <f>D26*E26</f>
-        <v/>
-      </c>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26">
-        <f>IF(G26="","",ROUNDUP(D26/G26,0))</f>
-        <v/>
-      </c>
-      <c r="K26">
-        <f>IF(J26="","",J26*H26)</f>
-        <v/>
-      </c>
-      <c r="L26">
-        <f>IF(J26="","",J26*I26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea] / </t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>8809508850412</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>138</v>
-      </c>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27">
-        <f>D27*E27</f>
-        <v/>
-      </c>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
-      <c r="J27">
-        <f>IF(G27="","",ROUNDUP(D27/G27,0))</f>
-        <v/>
-      </c>
-      <c r="K27">
-        <f>IF(J27="","",J27*H27)</f>
-        <v/>
-      </c>
-      <c r="L27">
-        <f>IF(J27="","",J27*I27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ETUDEHOUSE</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ETUDE - Baking Powder BB Deep Cleansing Foam [30ml] / Пенка </t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>8809668028058</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>317</v>
-      </c>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28">
-        <f>D28*E28</f>
-        <v/>
-      </c>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
-      <c r="J28">
-        <f>IF(G28="","",ROUNDUP(D28/G28,0))</f>
-        <v/>
-      </c>
-      <c r="K28">
-        <f>IF(J28="","",J28*H28)</f>
-        <v/>
-      </c>
-      <c r="L28">
-        <f>IF(J28="","",J28*I28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>COSRX</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>COSRX - Advanced Snail 96 Mucin Power Essence [100ml] / Высо</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>8809416470009</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>414</v>
-      </c>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29">
-        <f>D29*E29</f>
-        <v/>
-      </c>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29">
-        <f>IF(G29="","",ROUNDUP(D29/G29,0))</f>
-        <v/>
-      </c>
-      <c r="K29">
-        <f>IF(J29="","",J29*H29)</f>
-        <v/>
-      </c>
-      <c r="L29">
-        <f>IF(J29="","",J29*I29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ROUND LAB VITA NIACINAMIDE DARK SPOT SERUM 30ml - Сыворотка </t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>8809962540652</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>337</v>
-      </c>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30">
-        <f>D30*E30</f>
-        <v/>
-      </c>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30">
-        <f>IF(G30="","",ROUNDUP(D30/G30,0))</f>
-        <v/>
-      </c>
-      <c r="K30">
-        <f>IF(J30="","",J30*H30)</f>
-        <v/>
-      </c>
-      <c r="L30">
-        <f>IF(J30="","",J30*I30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>DEOPROCE</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml] мягк</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>8809975191773</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>261</v>
-      </c>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31">
-        <f>D31*E31</f>
-        <v/>
-      </c>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31">
-        <f>IF(G31="","",ROUNDUP(D31/G31,0))</f>
-        <v/>
-      </c>
-      <c r="K31">
-        <f>IF(J31="","",J31*H31)</f>
-        <v/>
-      </c>
-      <c r="L31">
-        <f>IF(J31="","",J31*I31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ENOUGH - Collagen Moisture Foundation [Tone 23] / Тональный </t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>8809280062386</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>243</v>
-      </c>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32">
-        <f>D32*E32</f>
-        <v/>
-      </c>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32">
-        <f>IF(G32="","",ROUNDUP(D32/G32,0))</f>
-        <v/>
-      </c>
-      <c r="K32">
-        <f>IF(J32="","",J32*H32)</f>
-        <v/>
-      </c>
-      <c r="L32">
-        <f>IF(J32="","",J32*I32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>JIGOTT</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>JIGOTT - Collagen Healing Cream [100ml] / Крем для лица с ко</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>8809210036524</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>177</v>
-      </c>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33">
-        <f>D33*E33</f>
-        <v/>
-      </c>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33">
-        <f>IF(G33="","",ROUNDUP(D33/G33,0))</f>
-        <v/>
-      </c>
-      <c r="K33">
-        <f>IF(J33="","",J33*H33)</f>
-        <v/>
-      </c>
-      <c r="L33">
-        <f>IF(J33="","",J33*I33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml - Сыворотка для жир</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>8809783325667</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>201</v>
-      </c>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34">
-        <f>D34*E34</f>
-        <v/>
-      </c>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34">
-        <f>IF(G34="","",ROUNDUP(D34/G34,0))</f>
-        <v/>
-      </c>
-      <c r="K34">
-        <f>IF(J34="","",J34*H34)</f>
-        <v/>
-      </c>
-      <c r="L34">
-        <f>IF(J34="","",J34*I34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>DEOPROCE</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC INTENSME ENERGY [600ml] мягк</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>8809975191766</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>157</v>
-      </c>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35">
-        <f>D35*E35</f>
-        <v/>
-      </c>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35">
-        <f>IF(G35="","",ROUNDUP(D35/G35,0))</f>
-        <v/>
-      </c>
-      <c r="K35">
-        <f>IF(J35="","",J35*H35)</f>
-        <v/>
-      </c>
-      <c r="L35">
-        <f>IF(J35="","",J35*I35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>DEOPROCE</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>DEOPROCE - SNAIL RECOVERY CREAM [100g] / Крем восстанавливаю</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>8809240760659</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>164</v>
-      </c>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36">
-        <f>D36*E36</f>
-        <v/>
-      </c>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36">
-        <f>IF(G36="","",ROUNDUP(D36/G36,0))</f>
-        <v/>
-      </c>
-      <c r="K36">
-        <f>IF(J36="","",J36*H36)</f>
-        <v/>
-      </c>
-      <c r="L36">
-        <f>IF(J36="","",J36*I36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TheOrdinary</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>THE ORDINARY - Argireline Solution 10% [30ml] / Сыворотка дл</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>769915190946</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>88</v>
-      </c>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37">
-        <f>D37*E37</f>
-        <v/>
-      </c>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37">
-        <f>IF(G37="","",ROUNDUP(D37/G37,0))</f>
-        <v/>
-      </c>
-      <c r="K37">
-        <f>IF(J37="","",J37*H37)</f>
-        <v/>
-      </c>
-      <c r="L37">
-        <f>IF(J37="","",J37*I37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>8809508850801</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>72</v>
-      </c>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38">
-        <f>D38*E38</f>
-        <v/>
-      </c>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38">
-        <f>IF(G38="","",ROUNDUP(D38/G38,0))</f>
-        <v/>
-      </c>
-      <c r="K38">
-        <f>IF(J38="","",J38*H38)</f>
-        <v/>
-      </c>
-      <c r="L38">
-        <f>IF(J38="","",J38*I38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>LEBELAGE</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LEBELAGE - Dr. Hyaluronic Derma Eye Cream [40ml] / Крем для </t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>8809445616522</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>152</v>
-      </c>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39">
-        <f>D39*E39</f>
-        <v/>
-      </c>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39">
-        <f>IF(G39="","",ROUNDUP(D39/G39,0))</f>
-        <v/>
-      </c>
-      <c r="K39">
-        <f>IF(J39="","",J39*H39)</f>
-        <v/>
-      </c>
-      <c r="L39">
-        <f>IF(J39="","",J39*I39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ISNTREE</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>ISNTREE - Chestnut AHA 8% Clear Essence Sample [20ml] / Увла</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>8809088970357</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>85</v>
-      </c>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40">
-        <f>D40*E40</f>
-        <v/>
-      </c>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40">
-        <f>IF(G40="","",ROUNDUP(D40/G40,0))</f>
-        <v/>
-      </c>
-      <c r="K40">
-        <f>IF(J40="","",J40*H40)</f>
-        <v/>
-      </c>
-      <c r="L40">
-        <f>IF(J40="","",J40*I40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>ROUND LAB SOYBEAN CLEANSING OIL_200ml - Гидрофильное масло д</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>8809783322130</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>112</v>
-      </c>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41">
-        <f>D41*E41</f>
-        <v/>
-      </c>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41">
-        <f>IF(G41="","",ROUNDUP(D41/G41,0))</f>
-        <v/>
-      </c>
-      <c r="K41">
-        <f>IF(J41="","",J41*H41)</f>
-        <v/>
-      </c>
-      <c r="L41">
-        <f>IF(J41="","",J41*I41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>ENOUGH</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02 [9g]/Конси</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>8809605872270</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>71</v>
-      </c>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42">
-        <f>D42*E42</f>
-        <v/>
-      </c>
-      <c r="G42" s="2" t="n"/>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42">
-        <f>IF(G42="","",ROUNDUP(D42/G42,0))</f>
-        <v/>
-      </c>
-      <c r="K42">
-        <f>IF(J42="","",J42*H42)</f>
-        <v/>
-      </c>
-      <c r="L42">
-        <f>IF(J42="","",J42*I42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="D43" s="1">
-        <f>SUM(D2:D42)</f>
-        <v/>
-      </c>
-      <c r="F43" s="1">
-        <f>SUM(F2:F42)</f>
-        <v/>
-      </c>
-      <c r="K43" s="1">
-        <f>SUM(K2:K42)</f>
-        <v/>
-      </c>
-      <c r="L43" s="1">
-        <f>SUM(L2:L42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Вес контейнера, т</t>
-        </is>
-      </c>
-      <c r="D45">
-        <f>L43/1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Лимит 26т/120к шт | транзит 2 мес | цель 6 мес | FarmStay искл. Жёлтые=ввод цены/короба (нет в заказе 22.06).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>